--- a/site/exports/hit-shenzhen-ic.xlsx
+++ b/site/exports/hit-shenzhen-ic.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R462dcedfb73f4abb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Re4004fa80baf45f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R4b0c3afb7b44455d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R120691efbcc24a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R3a3ba9bcd6af4081"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R42d2b2a480d74550"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rf27eba33949d424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R60e46853139445e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R1258b71240ab40fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R2522062e50fe49ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T2_0" displayName="T2_0" ref="A1:G35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T3_0" displayName="T3_0" ref="A1:G35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T2_1" displayName="T2_1" ref="A1:Q234" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T3_1" displayName="T3_1" ref="A1:Q235" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T2_2" displayName="T2_2" ref="A1:J34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T3_2" displayName="T3_2" ref="A1:J34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T2_3" displayName="T2_3" ref="A1:J48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T3_3" displayName="T3_3" ref="A1:J48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T2_4" displayName="T2_4" ref="A1:E142" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T3_4" displayName="T3_4" ref="A1:E142" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -1239,7 +1239,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdffb0872ff2140a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ab1adc560b4167"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8808,51 +8808,37 @@
     </x:row>
     <x:row r="196" ht="64" customHeight="1">
       <x:c r="A196" s="6" t="str">
-        <x:v>陈文君</x:v>
+        <x:v>张明宇</x:v>
       </x:c>
       <x:c r="B196" s="6" t="str">
-        <x:v>degree</x:v>
+        <x:v>research_assistant_collaborator</x:v>
       </x:c>
       <x:c r="C196" s="6" t="str">
-        <x:v>学士</x:v>
+        <x:v>研究助理阶段合作教授</x:v>
       </x:c>
       <x:c r="D196" s="6" t="str">
-        <x:v>大连理工大学</x:v>
+        <x:v>清华大学微纳米力学与多学科交叉创新研究中心</x:v>
       </x:c>
       <x:c r="E196" s="6" t="str">
-        <x:v>2009-09</x:v>
+        <x:v>2014-03</x:v>
       </x:c>
       <x:c r="F196" s="6" t="str">
-        <x:v>2013-07</x:v>
-      </x:c>
-      <x:c r="G196" s="6" t="str">
-        <x:v>Materials Processing and Control Engineering</x:v>
-      </x:c>
-      <x:c r="H196" s="6" t="str">
-        <x:v>中国</x:v>
-      </x:c>
-      <x:c r="I196" s="6" t="str">
-        <x:v>中国内地</x:v>
-      </x:c>
-      <x:c r="J196" s="6" t="str">
-        <x:v>亚洲</x:v>
-      </x:c>
-      <x:c r="K196" s="6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="L196" s="13" t="b">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>2014-08</x:v>
+      </x:c>
+      <x:c r="G196" s="6" t="str"/>
+      <x:c r="H196" s="6" t="str"/>
+      <x:c r="I196" s="6" t="str"/>
+      <x:c r="J196" s="6" t="str"/>
+      <x:c r="K196" s="6" t="str"/>
+      <x:c r="L196" s="6" t="str"/>
       <x:c r="M196" s="7" t="str"/>
       <x:c r="N196" s="6" t="str"/>
       <x:c r="O196" s="6" t="str">
-        <x:v>博士论文VITA xii页。</x:v>
-      </x:c>
-      <x:c r="P196" s="6" t="str">
-        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问分开。</x:v>
-      </x:c>
+        <x:v>张莹莹；清华大学化学系教授、博士生导师，研究柔性可穿戴器件。；本人履历仅写合作教授，单列为研究合作，不声称学位导师。；非导师认定，不计师承；https://www.chem.tsinghua.edu.cn/info/1107/2644.htm</x:v>
+      </x:c>
+      <x:c r="P196" s="6" t="str"/>
       <x:c r="Q196" s="6" t="str">
-        <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
+        <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="64" customHeight="1">
@@ -8863,31 +8849,31 @@
         <x:v>degree</x:v>
       </x:c>
       <x:c r="C197" s="6" t="str">
-        <x:v>硕士</x:v>
+        <x:v>学士</x:v>
       </x:c>
       <x:c r="D197" s="6" t="str">
-        <x:v>加州大学默塞德分校</x:v>
+        <x:v>大连理工大学</x:v>
       </x:c>
       <x:c r="E197" s="6" t="str">
-        <x:v>2013-09</x:v>
+        <x:v>2009-09</x:v>
       </x:c>
       <x:c r="F197" s="6" t="str">
-        <x:v>2015-05</x:v>
+        <x:v>2013-07</x:v>
       </x:c>
       <x:c r="G197" s="6" t="str">
-        <x:v>Mechanical Engineering</x:v>
+        <x:v>Materials Processing and Control Engineering</x:v>
       </x:c>
       <x:c r="H197" s="6" t="str">
-        <x:v>美国</x:v>
+        <x:v>中国</x:v>
       </x:c>
       <x:c r="I197" s="6" t="str">
-        <x:v>美国</x:v>
+        <x:v>中国内地</x:v>
       </x:c>
       <x:c r="J197" s="6" t="str">
-        <x:v>北美洲</x:v>
+        <x:v>亚洲</x:v>
       </x:c>
       <x:c r="K197" s="6" t="str">
-        <x:v>no</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="L197" s="13" t="b">
         <x:v>1</x:v>
@@ -8912,19 +8898,19 @@
         <x:v>degree</x:v>
       </x:c>
       <x:c r="C198" s="6" t="str">
-        <x:v>博士</x:v>
+        <x:v>硕士</x:v>
       </x:c>
       <x:c r="D198" s="6" t="str">
-        <x:v>加州大学圣地亚哥分校</x:v>
+        <x:v>加州大学默塞德分校</x:v>
       </x:c>
       <x:c r="E198" s="6" t="str">
-        <x:v>2015-09</x:v>
+        <x:v>2013-09</x:v>
       </x:c>
       <x:c r="F198" s="6" t="str">
-        <x:v>2019-12</x:v>
+        <x:v>2015-05</x:v>
       </x:c>
       <x:c r="G198" s="6" t="str">
-        <x:v>Materials Science and Engineering</x:v>
+        <x:v>Mechanical Engineering</x:v>
       </x:c>
       <x:c r="H198" s="6" t="str">
         <x:v>美国</x:v>
@@ -8944,7 +8930,7 @@
       <x:c r="M198" s="7" t="str"/>
       <x:c r="N198" s="6" t="str"/>
       <x:c r="O198" s="6" t="str">
-        <x:v>论文VITA给学习区间，封面与HIT官网确认2019博士，不另推精确授位日。</x:v>
+        <x:v>博士论文VITA xii页。</x:v>
       </x:c>
       <x:c r="P198" s="6" t="str">
         <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问分开。</x:v>
@@ -8958,30 +8944,48 @@
         <x:v>陈文君</x:v>
       </x:c>
       <x:c r="B199" s="6" t="str">
-        <x:v>employment</x:v>
+        <x:v>degree</x:v>
       </x:c>
       <x:c r="C199" s="6" t="str">
-        <x:v>Assistant Professor</x:v>
+        <x:v>博士</x:v>
       </x:c>
       <x:c r="D199" s="6" t="str">
-        <x:v>哈尔滨工业大学（深圳）</x:v>
-      </x:c>
-      <x:c r="E199" s="6" t="str"/>
-      <x:c r="F199" s="6" t="str"/>
-      <x:c r="G199" s="6" t="str"/>
-      <x:c r="H199" s="6" t="str"/>
-      <x:c r="I199" s="6" t="str"/>
-      <x:c r="J199" s="6" t="str"/>
-      <x:c r="K199" s="6" t="str"/>
-      <x:c r="L199" s="6" t="str"/>
+        <x:v>加州大学圣地亚哥分校</x:v>
+      </x:c>
+      <x:c r="E199" s="6" t="str">
+        <x:v>2015-09</x:v>
+      </x:c>
+      <x:c r="F199" s="6" t="str">
+        <x:v>2019-12</x:v>
+      </x:c>
+      <x:c r="G199" s="6" t="str">
+        <x:v>Materials Science and Engineering</x:v>
+      </x:c>
+      <x:c r="H199" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I199" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J199" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K199" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L199" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M199" s="7" t="str"/>
       <x:c r="N199" s="6" t="str"/>
       <x:c r="O199" s="6" t="str">
-        <x:v>英文个人简介现列Assistant Professor；学院副教授名录与其冲突，未擅自映射职级。</x:v>
-      </x:c>
-      <x:c r="P199" s="6" t="str"/>
+        <x:v>论文VITA给学习区间，封面与HIT官网确认2019博士，不另推精确授位日。</x:v>
+      </x:c>
+      <x:c r="P199" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位与访问分开。</x:v>
+      </x:c>
       <x:c r="Q199" s="6" t="str">
-        <x:v>https://homepage.hit.edu.cn/WenjunChen</x:v>
+        <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="64" customHeight="1">
@@ -8992,10 +8996,10 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C200" s="6" t="str">
-        <x:v>副教授（名录类别）</x:v>
+        <x:v>Assistant Professor</x:v>
       </x:c>
       <x:c r="D200" s="6" t="str">
-        <x:v>哈尔滨工业大学（深圳）集成电路学院</x:v>
+        <x:v>哈尔滨工业大学（深圳）</x:v>
       </x:c>
       <x:c r="E200" s="6" t="str"/>
       <x:c r="F200" s="6" t="str"/>
@@ -9008,11 +9012,11 @@
       <x:c r="M200" s="7" t="str"/>
       <x:c r="N200" s="6" t="str"/>
       <x:c r="O200" s="6" t="str">
-        <x:v>名录类别与个人英文Assistant Professor不一致，现职级待核。</x:v>
+        <x:v>英文个人简介现列Assistant Professor；学院副教授名录与其冲突，未擅自映射职级。</x:v>
       </x:c>
       <x:c r="P200" s="6" t="str"/>
       <x:c r="Q200" s="6" t="str">
-        <x:v>https://ic.hitsz.edu.cn/szll/qzjs/fjs.htm</x:v>
+        <x:v>https://homepage.hit.edu.cn/WenjunChen</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="64" customHeight="1">
@@ -9023,14 +9027,12 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C201" s="6" t="str">
-        <x:v>Graduate Researcher</x:v>
+        <x:v>副教授（名录类别）</x:v>
       </x:c>
       <x:c r="D201" s="6" t="str">
-        <x:v>加州大学圣地亚哥分校 Oscar Vazquez-Mena Lab</x:v>
-      </x:c>
-      <x:c r="E201" s="6" t="str">
-        <x:v>2015-09</x:v>
-      </x:c>
+        <x:v>哈尔滨工业大学（深圳）集成电路学院</x:v>
+      </x:c>
+      <x:c r="E201" s="6" t="str"/>
       <x:c r="F201" s="6" t="str"/>
       <x:c r="G201" s="6" t="str"/>
       <x:c r="H201" s="6" t="str"/>
@@ -9041,11 +9043,11 @@
       <x:c r="M201" s="7" t="str"/>
       <x:c r="N201" s="6" t="str"/>
       <x:c r="O201" s="6" t="str">
-        <x:v>论文VITA写2015-09至Present，Present指2019论文写作时，不表示当前仍在任；结束时间未披露。</x:v>
+        <x:v>名录类别与个人英文Assistant Professor不一致，现职级待核。</x:v>
       </x:c>
       <x:c r="P201" s="6" t="str"/>
       <x:c r="Q201" s="6" t="str">
-        <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
+        <x:v>https://ic.hitsz.edu.cn/szll/qzjs/fjs.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="64" customHeight="1">
@@ -9059,14 +9061,12 @@
         <x:v>Graduate Researcher</x:v>
       </x:c>
       <x:c r="D202" s="6" t="str">
-        <x:v>加州大学默塞德分校 Vincent C. Tung Lab</x:v>
+        <x:v>加州大学圣地亚哥分校 Oscar Vazquez-Mena Lab</x:v>
       </x:c>
       <x:c r="E202" s="6" t="str">
-        <x:v>2014-01</x:v>
-      </x:c>
-      <x:c r="F202" s="6" t="str">
-        <x:v>2015-05</x:v>
-      </x:c>
+        <x:v>2015-09</x:v>
+      </x:c>
+      <x:c r="F202" s="6" t="str"/>
       <x:c r="G202" s="6" t="str"/>
       <x:c r="H202" s="6" t="str"/>
       <x:c r="I202" s="6" t="str"/>
@@ -9076,7 +9076,7 @@
       <x:c r="M202" s="7" t="str"/>
       <x:c r="N202" s="6" t="str"/>
       <x:c r="O202" s="6" t="str">
-        <x:v>课题组研究身份，不据此推定硕士导师。</x:v>
+        <x:v>论文VITA写2015-09至Present，Present指2019论文写作时，不表示当前仍在任；结束时间未披露。</x:v>
       </x:c>
       <x:c r="P202" s="6" t="str"/>
       <x:c r="Q202" s="6" t="str">
@@ -9091,16 +9091,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C203" s="6" t="str">
-        <x:v>Teaching Assistant</x:v>
+        <x:v>Graduate Researcher</x:v>
       </x:c>
       <x:c r="D203" s="6" t="str">
-        <x:v>加州大学圣地亚哥分校</x:v>
+        <x:v>加州大学默塞德分校 Vincent C. Tung Lab</x:v>
       </x:c>
       <x:c r="E203" s="6" t="str">
-        <x:v>2017</x:v>
+        <x:v>2014-01</x:v>
       </x:c>
       <x:c r="F203" s="6" t="str">
-        <x:v>2019</x:v>
+        <x:v>2015-05</x:v>
       </x:c>
       <x:c r="G203" s="6" t="str"/>
       <x:c r="H203" s="6" t="str"/>
@@ -9111,7 +9111,7 @@
       <x:c r="M203" s="7" t="str"/>
       <x:c r="N203" s="6" t="str"/>
       <x:c r="O203" s="6" t="str">
-        <x:v>论文列Winter 2017/2018/2019，不表示连续全职任职。</x:v>
+        <x:v>课题组研究身份，不据此推定硕士导师。</x:v>
       </x:c>
       <x:c r="P203" s="6" t="str"/>
       <x:c r="Q203" s="6" t="str">
@@ -9129,13 +9129,13 @@
         <x:v>Teaching Assistant</x:v>
       </x:c>
       <x:c r="D204" s="6" t="str">
-        <x:v>加州大学默塞德分校</x:v>
+        <x:v>加州大学圣地亚哥分校</x:v>
       </x:c>
       <x:c r="E204" s="6" t="str">
-        <x:v>2013</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="F204" s="6" t="str">
-        <x:v>2015</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="G204" s="6" t="str"/>
       <x:c r="H204" s="6" t="str"/>
@@ -9146,7 +9146,7 @@
       <x:c r="M204" s="7" t="str"/>
       <x:c r="N204" s="6" t="str"/>
       <x:c r="O204" s="6" t="str">
-        <x:v>论文列2013/2014/2015。</x:v>
+        <x:v>论文列Winter 2017/2018/2019，不表示连续全职任职。</x:v>
       </x:c>
       <x:c r="P204" s="6" t="str"/>
       <x:c r="Q204" s="6" t="str">
@@ -9161,16 +9161,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C205" s="6" t="str">
-        <x:v>实习</x:v>
+        <x:v>Teaching Assistant</x:v>
       </x:c>
       <x:c r="D205" s="6" t="str">
-        <x:v>FAW Automobile Co., Ltd</x:v>
+        <x:v>加州大学默塞德分校</x:v>
       </x:c>
       <x:c r="E205" s="6" t="str">
-        <x:v>2012-07</x:v>
+        <x:v>2013</x:v>
       </x:c>
       <x:c r="F205" s="6" t="str">
-        <x:v>2012-09</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="G205" s="6" t="str"/>
       <x:c r="H205" s="6" t="str"/>
@@ -9180,7 +9180,9 @@
       <x:c r="L205" s="6" t="str"/>
       <x:c r="M205" s="7" t="str"/>
       <x:c r="N205" s="6" t="str"/>
-      <x:c r="O205" s="6" t="str"/>
+      <x:c r="O205" s="6" t="str">
+        <x:v>论文列2013/2014/2015。</x:v>
+      </x:c>
       <x:c r="P205" s="6" t="str"/>
       <x:c r="Q205" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
@@ -9197,13 +9199,13 @@
         <x:v>实习</x:v>
       </x:c>
       <x:c r="D206" s="6" t="str">
-        <x:v>Chemical Fiber Group Co., Ltd</x:v>
+        <x:v>FAW Automobile Co., Ltd</x:v>
       </x:c>
       <x:c r="E206" s="6" t="str">
-        <x:v>2010-07</x:v>
+        <x:v>2012-07</x:v>
       </x:c>
       <x:c r="F206" s="6" t="str">
-        <x:v>2010-08</x:v>
+        <x:v>2012-09</x:v>
       </x:c>
       <x:c r="G206" s="6" t="str"/>
       <x:c r="H206" s="6" t="str"/>
@@ -9213,9 +9215,7 @@
       <x:c r="L206" s="6" t="str"/>
       <x:c r="M206" s="7" t="str"/>
       <x:c r="N206" s="6" t="str"/>
-      <x:c r="O206" s="6" t="str">
-        <x:v>机构原文未给更多身份，不自行扩写。</x:v>
-      </x:c>
+      <x:c r="O206" s="6" t="str"/>
       <x:c r="P206" s="6" t="str"/>
       <x:c r="Q206" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
@@ -9223,49 +9223,37 @@
     </x:row>
     <x:row r="207" ht="64" customHeight="1">
       <x:c r="A207" s="6" t="str">
-        <x:v>祝温泊</x:v>
+        <x:v>陈文君</x:v>
       </x:c>
       <x:c r="B207" s="6" t="str">
-        <x:v>degree</x:v>
+        <x:v>employment</x:v>
       </x:c>
       <x:c r="C207" s="6" t="str">
-        <x:v>学士</x:v>
+        <x:v>实习</x:v>
       </x:c>
       <x:c r="D207" s="6" t="str">
-        <x:v>华中科技大学</x:v>
+        <x:v>Chemical Fiber Group Co., Ltd</x:v>
       </x:c>
       <x:c r="E207" s="6" t="str">
-        <x:v>2006-09</x:v>
+        <x:v>2010-07</x:v>
       </x:c>
       <x:c r="F207" s="6" t="str">
-        <x:v>2010-06</x:v>
-      </x:c>
-      <x:c r="G207" s="6" t="str">
-        <x:v>材料成型及控制工程</x:v>
-      </x:c>
-      <x:c r="H207" s="6" t="str">
-        <x:v>中国</x:v>
-      </x:c>
-      <x:c r="I207" s="6" t="str">
-        <x:v>中国内地</x:v>
-      </x:c>
-      <x:c r="J207" s="6" t="str">
-        <x:v>亚洲</x:v>
-      </x:c>
-      <x:c r="K207" s="6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="L207" s="13" t="b">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>2010-08</x:v>
+      </x:c>
+      <x:c r="G207" s="6" t="str"/>
+      <x:c r="H207" s="6" t="str"/>
+      <x:c r="I207" s="6" t="str"/>
+      <x:c r="J207" s="6" t="str"/>
+      <x:c r="K207" s="6" t="str"/>
+      <x:c r="L207" s="6" t="str"/>
       <x:c r="M207" s="7" t="str"/>
       <x:c r="N207" s="6" t="str"/>
-      <x:c r="O207" s="6" t="str"/>
-      <x:c r="P207" s="6" t="str">
-        <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
-      </x:c>
+      <x:c r="O207" s="6" t="str">
+        <x:v>机构原文未给更多身份，不自行扩写。</x:v>
+      </x:c>
+      <x:c r="P207" s="6" t="str"/>
       <x:c r="Q207" s="6" t="str">
-        <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
+        <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="64" customHeight="1">
@@ -9276,19 +9264,19 @@
         <x:v>degree</x:v>
       </x:c>
       <x:c r="C208" s="6" t="str">
-        <x:v>博士</x:v>
+        <x:v>学士</x:v>
       </x:c>
       <x:c r="D208" s="6" t="str">
         <x:v>华中科技大学</x:v>
       </x:c>
       <x:c r="E208" s="6" t="str">
-        <x:v>2010-09</x:v>
+        <x:v>2006-09</x:v>
       </x:c>
       <x:c r="F208" s="6" t="str">
-        <x:v>2017-03</x:v>
+        <x:v>2010-06</x:v>
       </x:c>
       <x:c r="G208" s="6" t="str">
-        <x:v>材料加工工程</x:v>
+        <x:v>材料成型及控制工程</x:v>
       </x:c>
       <x:c r="H208" s="6" t="str">
         <x:v>中国</x:v>
@@ -9302,12 +9290,12 @@
       <x:c r="K208" s="6" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="L208" s="6" t="str"/>
+      <x:c r="L208" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M208" s="7" t="str"/>
       <x:c r="N208" s="6" t="str"/>
-      <x:c r="O208" s="6" t="str">
-        <x:v>官网列华中科技大学博士学习经历，与拉夫堡博士时间重叠；华科独立授位未获直接证实，degree_awarded保持null，不参与已确证博士授位统计，不推断联合培养或双学位。</x:v>
-      </x:c>
+      <x:c r="O208" s="6" t="str"/>
       <x:c r="P208" s="6" t="str">
         <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
       </x:c>
@@ -9326,35 +9314,35 @@
         <x:v>博士</x:v>
       </x:c>
       <x:c r="D209" s="6" t="str">
-        <x:v>Loughborough University</x:v>
+        <x:v>华中科技大学</x:v>
       </x:c>
       <x:c r="E209" s="6" t="str">
-        <x:v>2012-10</x:v>
+        <x:v>2010-09</x:v>
       </x:c>
       <x:c r="F209" s="6" t="str">
-        <x:v>2016-12</x:v>
+        <x:v>2017-03</x:v>
       </x:c>
       <x:c r="G209" s="6" t="str">
-        <x:v>Mechanical, Electrical and Manufacturing Engineering</x:v>
+        <x:v>材料加工工程</x:v>
       </x:c>
       <x:c r="H209" s="6" t="str">
-        <x:v>英国</x:v>
+        <x:v>中国</x:v>
       </x:c>
       <x:c r="I209" s="6" t="str">
-        <x:v>英国</x:v>
+        <x:v>中国内地</x:v>
       </x:c>
       <x:c r="J209" s="6" t="str">
-        <x:v>欧洲</x:v>
+        <x:v>亚洲</x:v>
       </x:c>
       <x:c r="K209" s="6" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="L209" s="13" t="b">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L209" s="6" t="str"/>
       <x:c r="M209" s="7" t="str"/>
       <x:c r="N209" s="6" t="str"/>
-      <x:c r="O209" s="6" t="str"/>
+      <x:c r="O209" s="6" t="str">
+        <x:v>官网列华中科技大学博士学习经历，与拉夫堡博士时间重叠；华科独立授位未获直接证实，degree_awarded保持null，不参与已确证博士授位统计，不推断联合培养或双学位。</x:v>
+      </x:c>
       <x:c r="P209" s="6" t="str">
         <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
       </x:c>
@@ -9367,30 +9355,44 @@
         <x:v>祝温泊</x:v>
       </x:c>
       <x:c r="B210" s="6" t="str">
-        <x:v>employment</x:v>
+        <x:v>degree</x:v>
       </x:c>
       <x:c r="C210" s="6" t="str">
-        <x:v>博士后</x:v>
+        <x:v>博士</x:v>
       </x:c>
       <x:c r="D210" s="6" t="str">
-        <x:v>哈尔滨工业大学（深圳）</x:v>
+        <x:v>Loughborough University</x:v>
       </x:c>
       <x:c r="E210" s="6" t="str">
-        <x:v>2017-07</x:v>
+        <x:v>2012-10</x:v>
       </x:c>
       <x:c r="F210" s="6" t="str">
-        <x:v>2020-01</x:v>
-      </x:c>
-      <x:c r="G210" s="6" t="str"/>
-      <x:c r="H210" s="6" t="str"/>
-      <x:c r="I210" s="6" t="str"/>
-      <x:c r="J210" s="6" t="str"/>
-      <x:c r="K210" s="6" t="str"/>
-      <x:c r="L210" s="6" t="str"/>
+        <x:v>2016-12</x:v>
+      </x:c>
+      <x:c r="G210" s="6" t="str">
+        <x:v>Mechanical, Electrical and Manufacturing Engineering</x:v>
+      </x:c>
+      <x:c r="H210" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="I210" s="6" t="str">
+        <x:v>英国</x:v>
+      </x:c>
+      <x:c r="J210" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K210" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L210" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M210" s="7" t="str"/>
       <x:c r="N210" s="6" t="str"/>
       <x:c r="O210" s="6" t="str"/>
-      <x:c r="P210" s="6" t="str"/>
+      <x:c r="P210" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
+      </x:c>
       <x:c r="Q210" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
       </x:c>
@@ -9403,16 +9405,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C211" s="6" t="str">
-        <x:v>助理研究员</x:v>
+        <x:v>博士后</x:v>
       </x:c>
       <x:c r="D211" s="6" t="str">
         <x:v>哈尔滨工业大学（深圳）</x:v>
       </x:c>
       <x:c r="E211" s="6" t="str">
-        <x:v>2020-05</x:v>
+        <x:v>2017-07</x:v>
       </x:c>
       <x:c r="F211" s="6" t="str">
-        <x:v>2022-05</x:v>
+        <x:v>2020-01</x:v>
       </x:c>
       <x:c r="G211" s="6" t="str"/>
       <x:c r="H211" s="6" t="str"/>
@@ -9436,16 +9438,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C212" s="6" t="str">
-        <x:v>助理教授</x:v>
+        <x:v>助理研究员</x:v>
       </x:c>
       <x:c r="D212" s="6" t="str">
         <x:v>哈尔滨工业大学（深圳）</x:v>
       </x:c>
       <x:c r="E212" s="6" t="str">
+        <x:v>2020-05</x:v>
+      </x:c>
+      <x:c r="F212" s="6" t="str">
         <x:v>2022-05</x:v>
-      </x:c>
-      <x:c r="F212" s="6" t="str">
-        <x:v>2024-04</x:v>
       </x:c>
       <x:c r="G212" s="6" t="str"/>
       <x:c r="H212" s="6" t="str"/>
@@ -9469,16 +9471,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C213" s="6" t="str">
-        <x:v>副教授</x:v>
+        <x:v>助理教授</x:v>
       </x:c>
       <x:c r="D213" s="6" t="str">
         <x:v>哈尔滨工业大学（深圳）</x:v>
       </x:c>
       <x:c r="E213" s="6" t="str">
-        <x:v>2024-05</x:v>
+        <x:v>2022-05</x:v>
       </x:c>
       <x:c r="F213" s="6" t="str">
-        <x:v>2026-01</x:v>
+        <x:v>2024-04</x:v>
       </x:c>
       <x:c r="G213" s="6" t="str"/>
       <x:c r="H213" s="6" t="str"/>
@@ -9502,15 +9504,17 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C214" s="6" t="str">
-        <x:v>教授</x:v>
+        <x:v>副教授</x:v>
       </x:c>
       <x:c r="D214" s="6" t="str">
         <x:v>哈尔滨工业大学（深圳）</x:v>
       </x:c>
       <x:c r="E214" s="6" t="str">
-        <x:v>2026-02</x:v>
-      </x:c>
-      <x:c r="F214" s="6" t="str"/>
+        <x:v>2024-05</x:v>
+      </x:c>
+      <x:c r="F214" s="6" t="str">
+        <x:v>2026-01</x:v>
+      </x:c>
       <x:c r="G214" s="6" t="str"/>
       <x:c r="H214" s="6" t="str"/>
       <x:c r="I214" s="6" t="str"/>
@@ -9527,47 +9531,33 @@
     </x:row>
     <x:row r="215" ht="64" customHeight="1">
       <x:c r="A215" s="6" t="str">
-        <x:v>刘飞华</x:v>
+        <x:v>祝温泊</x:v>
       </x:c>
       <x:c r="B215" s="6" t="str">
-        <x:v>degree</x:v>
+        <x:v>employment</x:v>
       </x:c>
       <x:c r="C215" s="6" t="str">
-        <x:v>工学学士</x:v>
+        <x:v>教授</x:v>
       </x:c>
       <x:c r="D215" s="6" t="str">
-        <x:v>武汉理工大学</x:v>
+        <x:v>哈尔滨工业大学（深圳）</x:v>
       </x:c>
       <x:c r="E215" s="6" t="str">
-        <x:v>2008-09</x:v>
-      </x:c>
-      <x:c r="F215" s="6" t="str">
-        <x:v>2012-06</x:v>
-      </x:c>
+        <x:v>2026-02</x:v>
+      </x:c>
+      <x:c r="F215" s="6" t="str"/>
       <x:c r="G215" s="6" t="str"/>
-      <x:c r="H215" s="6" t="str">
-        <x:v>中国</x:v>
-      </x:c>
-      <x:c r="I215" s="6" t="str">
-        <x:v>中国内地</x:v>
-      </x:c>
-      <x:c r="J215" s="6" t="str">
-        <x:v>亚洲</x:v>
-      </x:c>
-      <x:c r="K215" s="6" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="L215" s="13" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="H215" s="6" t="str"/>
+      <x:c r="I215" s="6" t="str"/>
+      <x:c r="J215" s="6" t="str"/>
+      <x:c r="K215" s="6" t="str"/>
+      <x:c r="L215" s="6" t="str"/>
       <x:c r="M215" s="7" t="str"/>
       <x:c r="N215" s="6" t="str"/>
       <x:c r="O215" s="6" t="str"/>
-      <x:c r="P215" s="6" t="str">
-        <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
-      </x:c>
+      <x:c r="P215" s="6" t="str"/>
       <x:c r="Q215" s="6" t="str">
-        <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
+        <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="64" customHeight="1">
@@ -9578,16 +9568,16 @@
         <x:v>degree</x:v>
       </x:c>
       <x:c r="C216" s="6" t="str">
-        <x:v>工学博士</x:v>
+        <x:v>工学学士</x:v>
       </x:c>
       <x:c r="D216" s="6" t="str">
         <x:v>武汉理工大学</x:v>
       </x:c>
       <x:c r="E216" s="6" t="str">
-        <x:v>2012-09</x:v>
+        <x:v>2008-09</x:v>
       </x:c>
       <x:c r="F216" s="6" t="str">
-        <x:v>2018-06</x:v>
+        <x:v>2012-06</x:v>
       </x:c>
       <x:c r="G216" s="6" t="str"/>
       <x:c r="H216" s="6" t="str">
@@ -9620,39 +9610,39 @@
         <x:v>刘飞华</x:v>
       </x:c>
       <x:c r="B217" s="6" t="str">
-        <x:v>joint_training</x:v>
-      </x:c>
-      <x:c r="C217" s="6" t="str"/>
+        <x:v>degree</x:v>
+      </x:c>
+      <x:c r="C217" s="6" t="str">
+        <x:v>工学博士</x:v>
+      </x:c>
       <x:c r="D217" s="6" t="str">
-        <x:v>The Pennsylvania State University</x:v>
+        <x:v>武汉理工大学</x:v>
       </x:c>
       <x:c r="E217" s="6" t="str">
-        <x:v>2014-09</x:v>
+        <x:v>2012-09</x:v>
       </x:c>
       <x:c r="F217" s="6" t="str">
-        <x:v>2017-06</x:v>
+        <x:v>2018-06</x:v>
       </x:c>
       <x:c r="G217" s="6" t="str"/>
       <x:c r="H217" s="6" t="str">
-        <x:v>美国</x:v>
+        <x:v>中国</x:v>
       </x:c>
       <x:c r="I217" s="6" t="str">
-        <x:v>美国</x:v>
+        <x:v>中国内地</x:v>
       </x:c>
       <x:c r="J217" s="6" t="str">
-        <x:v>北美洲</x:v>
+        <x:v>亚洲</x:v>
       </x:c>
       <x:c r="K217" s="6" t="str">
         <x:v>no</x:v>
       </x:c>
       <x:c r="L217" s="13" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M217" s="7" t="str"/>
       <x:c r="N217" s="6" t="str"/>
-      <x:c r="O217" s="6" t="str">
-        <x:v>官网明确联合培养博士；不认定为美国博士授位。</x:v>
-      </x:c>
+      <x:c r="O217" s="6" t="str"/>
       <x:c r="P217" s="6" t="str">
         <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
       </x:c>
@@ -9665,30 +9655,42 @@
         <x:v>刘飞华</x:v>
       </x:c>
       <x:c r="B218" s="6" t="str">
-        <x:v>employment</x:v>
-      </x:c>
-      <x:c r="C218" s="6" t="str">
-        <x:v>Research Associate</x:v>
-      </x:c>
+        <x:v>joint_training</x:v>
+      </x:c>
+      <x:c r="C218" s="6" t="str"/>
       <x:c r="D218" s="6" t="str">
-        <x:v>The Pennsylvania State University，材料科学与工程</x:v>
+        <x:v>The Pennsylvania State University</x:v>
       </x:c>
       <x:c r="E218" s="6" t="str">
-        <x:v>2016-09</x:v>
+        <x:v>2014-09</x:v>
       </x:c>
       <x:c r="F218" s="6" t="str">
         <x:v>2017-06</x:v>
       </x:c>
       <x:c r="G218" s="6" t="str"/>
-      <x:c r="H218" s="6" t="str"/>
-      <x:c r="I218" s="6" t="str"/>
-      <x:c r="J218" s="6" t="str"/>
-      <x:c r="K218" s="6" t="str"/>
-      <x:c r="L218" s="6" t="str"/>
+      <x:c r="H218" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I218" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J218" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K218" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L218" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="M218" s="7" t="str"/>
       <x:c r="N218" s="6" t="str"/>
-      <x:c r="O218" s="6" t="str"/>
-      <x:c r="P218" s="6" t="str"/>
+      <x:c r="O218" s="6" t="str">
+        <x:v>官网明确联合培养博士；不认定为美国博士授位。</x:v>
+      </x:c>
+      <x:c r="P218" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
+      </x:c>
       <x:c r="Q218" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
       </x:c>
@@ -9701,16 +9703,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C219" s="6" t="str">
-        <x:v>研发总监/材料专家</x:v>
+        <x:v>Research Associate</x:v>
       </x:c>
       <x:c r="D219" s="6" t="str">
-        <x:v>深圳市信维通信股份有限公司中央研究院</x:v>
+        <x:v>The Pennsylvania State University，材料科学与工程</x:v>
       </x:c>
       <x:c r="E219" s="6" t="str">
-        <x:v>2018-07</x:v>
+        <x:v>2016-09</x:v>
       </x:c>
       <x:c r="F219" s="6" t="str">
-        <x:v>2021-06</x:v>
+        <x:v>2017-06</x:v>
       </x:c>
       <x:c r="G219" s="6" t="str"/>
       <x:c r="H219" s="6" t="str"/>
@@ -9734,16 +9736,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C220" s="6" t="str">
-        <x:v>助理研究员</x:v>
+        <x:v>研发总监/材料专家</x:v>
       </x:c>
       <x:c r="D220" s="6" t="str">
-        <x:v>哈尔滨工业大学（深圳）材料科学与工程学院</x:v>
+        <x:v>深圳市信维通信股份有限公司中央研究院</x:v>
       </x:c>
       <x:c r="E220" s="6" t="str">
+        <x:v>2018-07</x:v>
+      </x:c>
+      <x:c r="F220" s="6" t="str">
         <x:v>2021-06</x:v>
-      </x:c>
-      <x:c r="F220" s="6" t="str">
-        <x:v>2023-12</x:v>
       </x:c>
       <x:c r="G220" s="6" t="str"/>
       <x:c r="H220" s="6" t="str"/>
@@ -9770,13 +9772,13 @@
         <x:v>助理研究员</x:v>
       </x:c>
       <x:c r="D221" s="6" t="str">
-        <x:v>哈尔滨工业大学（深圳）集成电路学院</x:v>
+        <x:v>哈尔滨工业大学（深圳）材料科学与工程学院</x:v>
       </x:c>
       <x:c r="E221" s="6" t="str">
-        <x:v>2024-01</x:v>
+        <x:v>2021-06</x:v>
       </x:c>
       <x:c r="F221" s="6" t="str">
-        <x:v>2024-12</x:v>
+        <x:v>2023-12</x:v>
       </x:c>
       <x:c r="G221" s="6" t="str"/>
       <x:c r="H221" s="6" t="str"/>
@@ -9800,15 +9802,17 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C222" s="6" t="str">
-        <x:v>副研究员</x:v>
+        <x:v>助理研究员</x:v>
       </x:c>
       <x:c r="D222" s="6" t="str">
         <x:v>哈尔滨工业大学（深圳）集成电路学院</x:v>
       </x:c>
       <x:c r="E222" s="6" t="str">
+        <x:v>2024-01</x:v>
+      </x:c>
+      <x:c r="F222" s="6" t="str">
         <x:v>2024-12</x:v>
       </x:c>
-      <x:c r="F222" s="6" t="str"/>
       <x:c r="G222" s="6" t="str"/>
       <x:c r="H222" s="6" t="str"/>
       <x:c r="I222" s="6" t="str"/>
@@ -9825,47 +9829,33 @@
     </x:row>
     <x:row r="223" ht="64" customHeight="1">
       <x:c r="A223" s="6" t="str">
-        <x:v>李康</x:v>
+        <x:v>刘飞华</x:v>
       </x:c>
       <x:c r="B223" s="6" t="str">
-        <x:v>degree</x:v>
+        <x:v>employment</x:v>
       </x:c>
       <x:c r="C223" s="6" t="str">
-        <x:v>学士</x:v>
+        <x:v>副研究员</x:v>
       </x:c>
       <x:c r="D223" s="6" t="str">
-        <x:v>哈尔滨工业大学</x:v>
+        <x:v>哈尔滨工业大学（深圳）集成电路学院</x:v>
       </x:c>
       <x:c r="E223" s="6" t="str">
-        <x:v>2004-09</x:v>
-      </x:c>
-      <x:c r="F223" s="6" t="str">
-        <x:v>2008-07</x:v>
-      </x:c>
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="F223" s="6" t="str"/>
       <x:c r="G223" s="6" t="str"/>
-      <x:c r="H223" s="6" t="str">
-        <x:v>中国</x:v>
-      </x:c>
-      <x:c r="I223" s="6" t="str">
-        <x:v>中国内地</x:v>
-      </x:c>
-      <x:c r="J223" s="6" t="str">
-        <x:v>亚洲</x:v>
-      </x:c>
-      <x:c r="K223" s="6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="L223" s="13" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="H223" s="6" t="str"/>
+      <x:c r="I223" s="6" t="str"/>
+      <x:c r="J223" s="6" t="str"/>
+      <x:c r="K223" s="6" t="str"/>
+      <x:c r="L223" s="6" t="str"/>
       <x:c r="M223" s="7" t="str"/>
       <x:c r="N223" s="6" t="str"/>
       <x:c r="O223" s="6" t="str"/>
-      <x:c r="P223" s="6" t="str">
-        <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
-      </x:c>
+      <x:c r="P223" s="6" t="str"/>
       <x:c r="Q223" s="6" t="str">
-        <x:v>https://homepage.hit.edu.cn/likang</x:v>
+        <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="64" customHeight="1">
@@ -9876,16 +9866,16 @@
         <x:v>degree</x:v>
       </x:c>
       <x:c r="C224" s="6" t="str">
-        <x:v>博士</x:v>
+        <x:v>学士</x:v>
       </x:c>
       <x:c r="D224" s="6" t="str">
-        <x:v>中国科学院物理研究所</x:v>
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
       <x:c r="E224" s="6" t="str">
-        <x:v>2008-09</x:v>
+        <x:v>2004-09</x:v>
       </x:c>
       <x:c r="F224" s="6" t="str">
-        <x:v>2015-01</x:v>
+        <x:v>2008-07</x:v>
       </x:c>
       <x:c r="G224" s="6" t="str"/>
       <x:c r="H224" s="6" t="str">
@@ -9898,16 +9888,14 @@
         <x:v>亚洲</x:v>
       </x:c>
       <x:c r="K224" s="6" t="str">
-        <x:v>no</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="L224" s="13" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="M224" s="7" t="str"/>
       <x:c r="N224" s="6" t="str"/>
-      <x:c r="O224" s="6" t="str">
-        <x:v>官网以中科院物理研究所列学位经历；未将授位机构自动改成中国科学院大学。</x:v>
-      </x:c>
+      <x:c r="O224" s="6" t="str"/>
       <x:c r="P224" s="6" t="str">
         <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
       </x:c>
@@ -9920,30 +9908,44 @@
         <x:v>李康</x:v>
       </x:c>
       <x:c r="B225" s="6" t="str">
-        <x:v>employment</x:v>
+        <x:v>degree</x:v>
       </x:c>
       <x:c r="C225" s="6" t="str">
-        <x:v>博士后</x:v>
+        <x:v>博士</x:v>
       </x:c>
       <x:c r="D225" s="6" t="str">
-        <x:v>清华大学物理系</x:v>
+        <x:v>中国科学院物理研究所</x:v>
       </x:c>
       <x:c r="E225" s="6" t="str">
-        <x:v>2015-04</x:v>
+        <x:v>2008-09</x:v>
       </x:c>
       <x:c r="F225" s="6" t="str">
-        <x:v>2017-04</x:v>
+        <x:v>2015-01</x:v>
       </x:c>
       <x:c r="G225" s="6" t="str"/>
-      <x:c r="H225" s="6" t="str"/>
-      <x:c r="I225" s="6" t="str"/>
-      <x:c r="J225" s="6" t="str"/>
-      <x:c r="K225" s="6" t="str"/>
-      <x:c r="L225" s="6" t="str"/>
+      <x:c r="H225" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I225" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J225" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K225" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L225" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M225" s="7" t="str"/>
       <x:c r="N225" s="6" t="str"/>
-      <x:c r="O225" s="6" t="str"/>
-      <x:c r="P225" s="6" t="str"/>
+      <x:c r="O225" s="6" t="str">
+        <x:v>官网以中科院物理研究所列学位经历；未将授位机构自动改成中国科学院大学。</x:v>
+      </x:c>
+      <x:c r="P225" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
+      </x:c>
       <x:c r="Q225" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/likang</x:v>
       </x:c>
@@ -9956,16 +9958,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C226" s="6" t="str">
-        <x:v>技术总监</x:v>
+        <x:v>博士后</x:v>
       </x:c>
       <x:c r="D226" s="6" t="str">
-        <x:v>苏州来福易材料科技有限公司</x:v>
+        <x:v>清华大学物理系</x:v>
       </x:c>
       <x:c r="E226" s="6" t="str">
-        <x:v>2017-05</x:v>
+        <x:v>2015-04</x:v>
       </x:c>
       <x:c r="F226" s="6" t="str">
-        <x:v>2019-04</x:v>
+        <x:v>2017-04</x:v>
       </x:c>
       <x:c r="G226" s="6" t="str"/>
       <x:c r="H226" s="6" t="str"/>
@@ -9989,13 +9991,17 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C227" s="6" t="str">
-        <x:v>助理研究员</x:v>
+        <x:v>技术总监</x:v>
       </x:c>
       <x:c r="D227" s="6" t="str">
-        <x:v>哈尔滨工业大学（深圳）柔性印刷电子技术研究中心</x:v>
-      </x:c>
-      <x:c r="E227" s="6" t="str"/>
-      <x:c r="F227" s="6" t="str"/>
+        <x:v>苏州来福易材料科技有限公司</x:v>
+      </x:c>
+      <x:c r="E227" s="6" t="str">
+        <x:v>2017-05</x:v>
+      </x:c>
+      <x:c r="F227" s="6" t="str">
+        <x:v>2019-04</x:v>
+      </x:c>
       <x:c r="G227" s="6" t="str"/>
       <x:c r="H227" s="6" t="str"/>
       <x:c r="I227" s="6" t="str"/>
@@ -10004,9 +10010,7 @@
       <x:c r="L227" s="6" t="str"/>
       <x:c r="M227" s="7" t="str"/>
       <x:c r="N227" s="6" t="str"/>
-      <x:c r="O227" s="6" t="str">
-        <x:v>主页个人简介列此职称；名录列研究员类别，不将类别强制改成正研究员。</x:v>
-      </x:c>
+      <x:c r="O227" s="6" t="str"/>
       <x:c r="P227" s="6" t="str"/>
       <x:c r="Q227" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/likang</x:v>
@@ -10014,49 +10018,33 @@
     </x:row>
     <x:row r="228" ht="64" customHeight="1">
       <x:c r="A228" s="6" t="str">
-        <x:v>冯欢欢</x:v>
+        <x:v>李康</x:v>
       </x:c>
       <x:c r="B228" s="6" t="str">
-        <x:v>degree</x:v>
+        <x:v>employment</x:v>
       </x:c>
       <x:c r="C228" s="6" t="str">
-        <x:v>学士</x:v>
+        <x:v>助理研究员</x:v>
       </x:c>
       <x:c r="D228" s="6" t="str">
-        <x:v>北京师范大学</x:v>
-      </x:c>
-      <x:c r="E228" s="6" t="str">
-        <x:v>2002-09</x:v>
-      </x:c>
-      <x:c r="F228" s="6" t="str">
-        <x:v>2006-07</x:v>
-      </x:c>
-      <x:c r="G228" s="6" t="str">
-        <x:v>化学学院（院系名）</x:v>
-      </x:c>
-      <x:c r="H228" s="6" t="str">
-        <x:v>中国</x:v>
-      </x:c>
-      <x:c r="I228" s="6" t="str">
-        <x:v>中国内地</x:v>
-      </x:c>
-      <x:c r="J228" s="6" t="str">
-        <x:v>亚洲</x:v>
-      </x:c>
-      <x:c r="K228" s="6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="L228" s="13" t="b">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>哈尔滨工业大学（深圳）柔性印刷电子技术研究中心</x:v>
+      </x:c>
+      <x:c r="E228" s="6" t="str"/>
+      <x:c r="F228" s="6" t="str"/>
+      <x:c r="G228" s="6" t="str"/>
+      <x:c r="H228" s="6" t="str"/>
+      <x:c r="I228" s="6" t="str"/>
+      <x:c r="J228" s="6" t="str"/>
+      <x:c r="K228" s="6" t="str"/>
+      <x:c r="L228" s="6" t="str"/>
       <x:c r="M228" s="7" t="str"/>
       <x:c r="N228" s="6" t="str"/>
-      <x:c r="O228" s="6" t="str"/>
-      <x:c r="P228" s="6" t="str">
-        <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
-      </x:c>
+      <x:c r="O228" s="6" t="str">
+        <x:v>主页个人简介列此职称；名录列研究员类别，不将类别强制改成正研究员。</x:v>
+      </x:c>
+      <x:c r="P228" s="6" t="str"/>
       <x:c r="Q228" s="6" t="str">
-        <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
+        <x:v>https://homepage.hit.edu.cn/likang</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="64" customHeight="1">
@@ -10067,19 +10055,19 @@
         <x:v>degree</x:v>
       </x:c>
       <x:c r="C229" s="6" t="str">
-        <x:v>硕士</x:v>
+        <x:v>学士</x:v>
       </x:c>
       <x:c r="D229" s="6" t="str">
         <x:v>北京师范大学</x:v>
       </x:c>
       <x:c r="E229" s="6" t="str">
-        <x:v>2006-09</x:v>
+        <x:v>2002-09</x:v>
       </x:c>
       <x:c r="F229" s="6" t="str">
-        <x:v>2009-07</x:v>
+        <x:v>2006-07</x:v>
       </x:c>
       <x:c r="G229" s="6" t="str">
-        <x:v>高分子物理化学研究组（研究组名）</x:v>
+        <x:v>化学学院（院系名）</x:v>
       </x:c>
       <x:c r="H229" s="6" t="str">
         <x:v>中国</x:v>
@@ -10114,42 +10102,38 @@
         <x:v>degree</x:v>
       </x:c>
       <x:c r="C230" s="6" t="str">
-        <x:v>博士</x:v>
+        <x:v>硕士</x:v>
       </x:c>
       <x:c r="D230" s="6" t="str">
-        <x:v>Wageningen University</x:v>
+        <x:v>北京师范大学</x:v>
       </x:c>
       <x:c r="E230" s="6" t="str">
-        <x:v>2009-09</x:v>
+        <x:v>2006-09</x:v>
       </x:c>
       <x:c r="F230" s="6" t="str">
-        <x:v>2013-09</x:v>
+        <x:v>2009-07</x:v>
       </x:c>
       <x:c r="G230" s="6" t="str">
-        <x:v>Physical Chemistry and Soft Matter（机构名）</x:v>
+        <x:v>高分子物理化学研究组（研究组名）</x:v>
       </x:c>
       <x:c r="H230" s="6" t="str">
-        <x:v>荷兰</x:v>
+        <x:v>中国</x:v>
       </x:c>
       <x:c r="I230" s="6" t="str">
-        <x:v>荷兰</x:v>
+        <x:v>中国内地</x:v>
       </x:c>
       <x:c r="J230" s="6" t="str">
-        <x:v>欧洲</x:v>
+        <x:v>亚洲</x:v>
       </x:c>
       <x:c r="K230" s="6" t="str">
-        <x:v>no</x:v>
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="L230" s="13" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M230" s="7" t="d">
-        <x:v>2013-12-09T00:00:00.000Z</x:v>
-      </x:c>
+      <x:c r="M230" s="7" t="str"/>
       <x:c r="N230" s="6" t="str"/>
-      <x:c r="O230" s="6" t="str">
-        <x:v>HIT履历结束日期2013-09；WUR学位库明确授位2013-12-09，另存degree_awarded_date，不用履历结束日期代替授位日。</x:v>
-      </x:c>
+      <x:c r="O230" s="6" t="str"/>
       <x:c r="P230" s="6" t="str">
         <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
       </x:c>
@@ -10162,30 +10146,48 @@
         <x:v>冯欢欢</x:v>
       </x:c>
       <x:c r="B231" s="6" t="str">
-        <x:v>employment</x:v>
+        <x:v>degree</x:v>
       </x:c>
       <x:c r="C231" s="6" t="str">
-        <x:v>博士后</x:v>
+        <x:v>博士</x:v>
       </x:c>
       <x:c r="D231" s="6" t="str">
-        <x:v>Wageningen University，Physical Chemistry and Soft Matter</x:v>
+        <x:v>Wageningen University</x:v>
       </x:c>
       <x:c r="E231" s="6" t="str">
+        <x:v>2009-09</x:v>
+      </x:c>
+      <x:c r="F231" s="6" t="str">
         <x:v>2013-09</x:v>
       </x:c>
-      <x:c r="F231" s="6" t="str">
-        <x:v>2016-09</x:v>
-      </x:c>
-      <x:c r="G231" s="6" t="str"/>
-      <x:c r="H231" s="6" t="str"/>
-      <x:c r="I231" s="6" t="str"/>
-      <x:c r="J231" s="6" t="str"/>
-      <x:c r="K231" s="6" t="str"/>
-      <x:c r="L231" s="6" t="str"/>
-      <x:c r="M231" s="7" t="str"/>
+      <x:c r="G231" s="6" t="str">
+        <x:v>Physical Chemistry and Soft Matter（机构名）</x:v>
+      </x:c>
+      <x:c r="H231" s="6" t="str">
+        <x:v>荷兰</x:v>
+      </x:c>
+      <x:c r="I231" s="6" t="str">
+        <x:v>荷兰</x:v>
+      </x:c>
+      <x:c r="J231" s="6" t="str">
+        <x:v>欧洲</x:v>
+      </x:c>
+      <x:c r="K231" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L231" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M231" s="7" t="d">
+        <x:v>2013-12-09T00:00:00.000Z</x:v>
+      </x:c>
       <x:c r="N231" s="6" t="str"/>
-      <x:c r="O231" s="6" t="str"/>
-      <x:c r="P231" s="6" t="str"/>
+      <x:c r="O231" s="6" t="str">
+        <x:v>HIT履历结束日期2013-09；WUR学位库明确授位2013-12-09，另存degree_awarded_date，不用履历结束日期代替授位日。</x:v>
+      </x:c>
+      <x:c r="P231" s="6" t="str">
+        <x:v>按院校所在地标准化，不代表国籍；非授位访问与联合培养单列。</x:v>
+      </x:c>
       <x:c r="Q231" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
       </x:c>
@@ -10198,16 +10200,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C232" s="6" t="str">
-        <x:v>助理教授</x:v>
+        <x:v>博士后</x:v>
       </x:c>
       <x:c r="D232" s="6" t="str">
-        <x:v>哈尔滨工业大学（深圳）材料科学与工程学院</x:v>
+        <x:v>Wageningen University，Physical Chemistry and Soft Matter</x:v>
       </x:c>
       <x:c r="E232" s="6" t="str">
+        <x:v>2013-09</x:v>
+      </x:c>
+      <x:c r="F232" s="6" t="str">
         <x:v>2016-09</x:v>
-      </x:c>
-      <x:c r="F232" s="6" t="str">
-        <x:v>2022-09</x:v>
       </x:c>
       <x:c r="G232" s="6" t="str"/>
       <x:c r="H232" s="6" t="str"/>
@@ -10231,16 +10233,16 @@
         <x:v>employment</x:v>
       </x:c>
       <x:c r="C233" s="6" t="str">
-        <x:v>副研究员</x:v>
+        <x:v>助理教授</x:v>
       </x:c>
       <x:c r="D233" s="6" t="str">
         <x:v>哈尔滨工业大学（深圳）材料科学与工程学院</x:v>
       </x:c>
       <x:c r="E233" s="6" t="str">
+        <x:v>2016-09</x:v>
+      </x:c>
+      <x:c r="F233" s="6" t="str">
         <x:v>2022-09</x:v>
-      </x:c>
-      <x:c r="F233" s="6" t="str">
-        <x:v>2024-06</x:v>
       </x:c>
       <x:c r="G233" s="6" t="str"/>
       <x:c r="H233" s="6" t="str"/>
@@ -10267,12 +10269,14 @@
         <x:v>副研究员</x:v>
       </x:c>
       <x:c r="D234" s="6" t="str">
-        <x:v>哈尔滨工业大学（深圳）集成电路学院</x:v>
+        <x:v>哈尔滨工业大学（深圳）材料科学与工程学院</x:v>
       </x:c>
       <x:c r="E234" s="6" t="str">
+        <x:v>2022-09</x:v>
+      </x:c>
+      <x:c r="F234" s="6" t="str">
         <x:v>2024-06</x:v>
       </x:c>
-      <x:c r="F234" s="6" t="str"/>
       <x:c r="G234" s="6" t="str"/>
       <x:c r="H234" s="6" t="str"/>
       <x:c r="I234" s="6" t="str"/>
@@ -10287,10 +10291,41 @@
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
       </x:c>
     </x:row>
+    <x:row r="235" ht="64" customHeight="1">
+      <x:c r="A235" s="6" t="str">
+        <x:v>冯欢欢</x:v>
+      </x:c>
+      <x:c r="B235" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C235" s="6" t="str">
+        <x:v>副研究员</x:v>
+      </x:c>
+      <x:c r="D235" s="6" t="str">
+        <x:v>哈尔滨工业大学（深圳）集成电路学院</x:v>
+      </x:c>
+      <x:c r="E235" s="6" t="str">
+        <x:v>2024-06</x:v>
+      </x:c>
+      <x:c r="F235" s="6" t="str"/>
+      <x:c r="G235" s="6" t="str"/>
+      <x:c r="H235" s="6" t="str"/>
+      <x:c r="I235" s="6" t="str"/>
+      <x:c r="J235" s="6" t="str"/>
+      <x:c r="K235" s="6" t="str"/>
+      <x:c r="L235" s="6" t="str"/>
+      <x:c r="M235" s="7" t="str"/>
+      <x:c r="N235" s="6" t="str"/>
+      <x:c r="O235" s="6" t="str"/>
+      <x:c r="P235" s="6" t="str"/>
+      <x:c r="Q235" s="6" t="str">
+        <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cf10e59ff494588"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc759782815714087"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11382,7 +11417,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ca7b80ca99d4082"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b76877c4c90494e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12848,7 +12883,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Recdb81b588484319"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re947935b5fa74edb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15281,7 +15316,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea61e84ad34b47ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d7c7a6f8ba4e87"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-ic.xlsx
+++ b/site/exports/hit-shenzhen-ic.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R42d2b2a480d74550"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rf27eba33949d424b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R60e46853139445e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R1258b71240ab40fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R2522062e50fe49ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcb79a5708d7e4a9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R43c295fe7d3c4592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R04cb78e69abe4bae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Ra22fa7f836ea46b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R873aa97cdfb2440d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T3_4" displayName="T3_4" ref="A1:E142" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T3_4" displayName="T3_4" ref="A1:E176" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -1239,7 +1239,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65ab1adc560b4167"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea561d142d3f4601"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10325,7 +10325,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc759782815714087"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58c09d9ff10744bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11417,7 +11417,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b76877c4c90494e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae7459f4e294cab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12883,7 +12883,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re947935b5fa74edb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2122b00a22054fd7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15313,10 +15313,588 @@
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
+    <x:row r="143" ht="64" customHeight="1">
+      <x:c r="A143" s="6" t="str">
+        <x:v>宋清海</x:v>
+      </x:c>
+      <x:c r="B143" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C143" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D143" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E143" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="64" customHeight="1">
+      <x:c r="A144" s="6" t="str">
+        <x:v>李明雨</x:v>
+      </x:c>
+      <x:c r="B144" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C144" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D144" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E144" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="64" customHeight="1">
+      <x:c r="A145" s="6" t="str">
+        <x:v>计红军</x:v>
+      </x:c>
+      <x:c r="B145" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C145" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D145" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E145" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="64" customHeight="1">
+      <x:c r="A146" s="6" t="str">
+        <x:v>马星</x:v>
+      </x:c>
+      <x:c r="B146" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C146" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D146" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E146" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="64" customHeight="1">
+      <x:c r="A147" s="6" t="str">
+        <x:v>王明江</x:v>
+      </x:c>
+      <x:c r="B147" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C147" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D147" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E147" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="64" customHeight="1">
+      <x:c r="A148" s="6" t="str">
+        <x:v>刘郝亮</x:v>
+      </x:c>
+      <x:c r="B148" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C148" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D148" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E148" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="64" customHeight="1">
+      <x:c r="A149" s="6" t="str">
+        <x:v>曲歌扬</x:v>
+      </x:c>
+      <x:c r="B149" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C149" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D149" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E149" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="64" customHeight="1">
+      <x:c r="A150" s="6" t="str">
+        <x:v>江智</x:v>
+      </x:c>
+      <x:c r="B150" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C150" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D150" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E150" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="64" customHeight="1">
+      <x:c r="A151" s="6" t="str">
+        <x:v>肖君军</x:v>
+      </x:c>
+      <x:c r="B151" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C151" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D151" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E151" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="64" customHeight="1">
+      <x:c r="A152" s="6" t="str">
+        <x:v>陈宏涛</x:v>
+      </x:c>
+      <x:c r="B152" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C152" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D152" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E152" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="64" customHeight="1">
+      <x:c r="A153" s="6" t="str">
+        <x:v>陈书湄</x:v>
+      </x:c>
+      <x:c r="B153" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C153" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D153" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E153" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="64" customHeight="1">
+      <x:c r="A154" s="6" t="str">
+        <x:v>陈怡沐</x:v>
+      </x:c>
+      <x:c r="B154" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C154" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D154" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E154" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="64" customHeight="1">
+      <x:c r="A155" s="6" t="str">
+        <x:v>周宇</x:v>
+      </x:c>
+      <x:c r="B155" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C155" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D155" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E155" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="64" customHeight="1">
+      <x:c r="A156" s="6" t="str">
+        <x:v>赵维巍</x:v>
+      </x:c>
+      <x:c r="B156" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C156" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D156" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E156" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="64" customHeight="1">
+      <x:c r="A157" s="6" t="str">
+        <x:v>钟颖</x:v>
+      </x:c>
+      <x:c r="B157" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C157" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D157" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E157" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="64" customHeight="1">
+      <x:c r="A158" s="6" t="str">
+        <x:v>徐科</x:v>
+      </x:c>
+      <x:c r="B158" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C158" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D158" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E158" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="64" customHeight="1">
+      <x:c r="A159" s="6" t="str">
+        <x:v>黄灿</x:v>
+      </x:c>
+      <x:c r="B159" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C159" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D159" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E159" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="64" customHeight="1">
+      <x:c r="A160" s="6" t="str">
+        <x:v>戴明志</x:v>
+      </x:c>
+      <x:c r="B160" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C160" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D160" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E160" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="64" customHeight="1">
+      <x:c r="A161" s="6" t="str">
+        <x:v>王嘉威</x:v>
+      </x:c>
+      <x:c r="B161" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C161" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D161" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E161" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="64" customHeight="1">
+      <x:c r="A162" s="6" t="str">
+        <x:v>王永杰</x:v>
+      </x:c>
+      <x:c r="B162" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C162" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D162" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E162" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="64" customHeight="1">
+      <x:c r="A163" s="6" t="str">
+        <x:v>金东东</x:v>
+      </x:c>
+      <x:c r="B163" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C163" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D163" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E163" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="64" customHeight="1">
+      <x:c r="A164" s="6" t="str">
+        <x:v>胡竞天</x:v>
+      </x:c>
+      <x:c r="B164" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C164" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D164" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E164" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="64" customHeight="1">
+      <x:c r="A165" s="6" t="str">
+        <x:v>秦敬凯</x:v>
+      </x:c>
+      <x:c r="B165" s="6" t="str">
+        <x:v>institution-classification-5</x:v>
+      </x:c>
+      <x:c r="C165" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D165" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E165" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="64" customHeight="1">
+      <x:c r="A166" s="6" t="str">
+        <x:v>崔爱娇</x:v>
+      </x:c>
+      <x:c r="B166" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C166" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D166" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E166" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="64" customHeight="1">
+      <x:c r="A167" s="6" t="str">
+        <x:v>王非</x:v>
+      </x:c>
+      <x:c r="B167" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C167" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D167" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E167" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="64" customHeight="1">
+      <x:c r="A168" s="6" t="str">
+        <x:v>王开阳</x:v>
+      </x:c>
+      <x:c r="B168" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C168" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D168" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E168" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="64" customHeight="1">
+      <x:c r="A169" s="6" t="str">
+        <x:v>阮琦锋</x:v>
+      </x:c>
+      <x:c r="B169" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C169" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D169" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E169" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="64" customHeight="1">
+      <x:c r="A170" s="6" t="str">
+        <x:v>李玉峰</x:v>
+      </x:c>
+      <x:c r="B170" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C170" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D170" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E170" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="64" customHeight="1">
+      <x:c r="A171" s="6" t="str">
+        <x:v>张明宇</x:v>
+      </x:c>
+      <x:c r="B171" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C171" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D171" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E171" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="64" customHeight="1">
+      <x:c r="A172" s="6" t="str">
+        <x:v>陈文君</x:v>
+      </x:c>
+      <x:c r="B172" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C172" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D172" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E172" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="64" customHeight="1">
+      <x:c r="A173" s="6" t="str">
+        <x:v>祝温泊</x:v>
+      </x:c>
+      <x:c r="B173" s="6" t="str">
+        <x:v>institution-classification-6</x:v>
+      </x:c>
+      <x:c r="C173" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D173" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E173" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="64" customHeight="1">
+      <x:c r="A174" s="6" t="str">
+        <x:v>刘飞华</x:v>
+      </x:c>
+      <x:c r="B174" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C174" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D174" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E174" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="64" customHeight="1">
+      <x:c r="A175" s="6" t="str">
+        <x:v>李康</x:v>
+      </x:c>
+      <x:c r="B175" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C175" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D175" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E175" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="64" customHeight="1">
+      <x:c r="A176" s="6" t="str">
+        <x:v>冯欢欢</x:v>
+      </x:c>
+      <x:c r="B176" s="6" t="str">
+        <x:v>institution-classification-7</x:v>
+      </x:c>
+      <x:c r="C176" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D176" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E176" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d7c7a6f8ba4e87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7887a1d285634422"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-ic.xlsx
+++ b/site/exports/hit-shenzhen-ic.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rcb79a5708d7e4a9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R43c295fe7d3c4592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R04cb78e69abe4bae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Ra22fa7f836ea46b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R873aa97cdfb2440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0f9f2f9058b8429c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rbccfebf6909b40df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rd10bf699e4fd4429"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Re6eff4c7f6294cf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R4b78f41e59284dc7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,8 +139,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T3_0" displayName="T3_0" ref="A1:G35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T3_0" displayName="T3_0" ref="A1:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
     <x:tableColumn id="3" name="院系"/>
@@ -148,6 +148,8 @@
     <x:tableColumn id="5" name="核对日期"/>
     <x:tableColumn id="6" name="缺项与冲突"/>
     <x:tableColumn id="7" name="范围"/>
+    <x:tableColumn id="8" name="主页可用性"/>
+    <x:tableColumn id="9" name="替代官方职业报道（非个人主页）"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -429,6 +431,8 @@
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -453,6 +457,12 @@
       <x:c r="G1" s="9" t="str">
         <x:v>范围</x:v>
       </x:c>
+      <x:c r="H1" s="9" t="str">
+        <x:v>主页可用性</x:v>
+      </x:c>
+      <x:c r="I1" s="9" t="str">
+        <x:v>替代官方职业报道（非个人主页）</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -476,6 +486,10 @@
       <x:c r="G2" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -499,6 +513,10 @@
       <x:c r="G3" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str"/>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -522,6 +540,10 @@
       <x:c r="G4" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str"/>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -545,6 +567,10 @@
       <x:c r="G5" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str"/>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -568,6 +594,10 @@
       <x:c r="G6" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str"/>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -591,6 +621,10 @@
       <x:c r="G7" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str"/>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -614,6 +648,10 @@
       <x:c r="G8" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str"/>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -637,6 +675,10 @@
       <x:c r="G9" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str"/>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -660,6 +702,10 @@
       <x:c r="G10" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str"/>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -683,6 +729,10 @@
       <x:c r="G11" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str"/>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -706,6 +756,10 @@
       <x:c r="G12" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str"/>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -729,6 +783,10 @@
       <x:c r="G13" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str"/>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -752,6 +810,10 @@
       <x:c r="G14" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str"/>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
       <x:c r="A15" s="6" t="str">
@@ -775,6 +837,10 @@
       <x:c r="G15" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I15" s="6" t="str"/>
     </x:row>
     <x:row r="16" ht="64" customHeight="1">
       <x:c r="A16" s="6" t="str">
@@ -798,6 +864,10 @@
       <x:c r="G16" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I16" s="6" t="str"/>
     </x:row>
     <x:row r="17" ht="64" customHeight="1">
       <x:c r="A17" s="6" t="str">
@@ -821,6 +891,10 @@
       <x:c r="G17" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I17" s="6" t="str"/>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
       <x:c r="A18" s="6" t="str">
@@ -844,6 +918,10 @@
       <x:c r="G18" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I18" s="6" t="str"/>
     </x:row>
     <x:row r="19" ht="64" customHeight="1">
       <x:c r="A19" s="6" t="str">
@@ -867,6 +945,10 @@
       <x:c r="G19" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H19" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I19" s="6" t="str"/>
     </x:row>
     <x:row r="20" ht="64" customHeight="1">
       <x:c r="A20" s="6" t="str">
@@ -890,6 +972,10 @@
       <x:c r="G20" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H20" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I20" s="6" t="str"/>
     </x:row>
     <x:row r="21" ht="64" customHeight="1">
       <x:c r="A21" s="6" t="str">
@@ -913,6 +999,10 @@
       <x:c r="G21" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H21" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I21" s="6" t="str"/>
     </x:row>
     <x:row r="22" ht="64" customHeight="1">
       <x:c r="A22" s="6" t="str">
@@ -936,6 +1026,10 @@
       <x:c r="G22" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H22" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I22" s="6" t="str"/>
     </x:row>
     <x:row r="23" ht="64" customHeight="1">
       <x:c r="A23" s="6" t="str">
@@ -959,6 +1053,10 @@
       <x:c r="G23" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H23" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I23" s="6" t="str"/>
     </x:row>
     <x:row r="24" ht="64" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -982,6 +1080,10 @@
       <x:c r="G24" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H24" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I24" s="6" t="str"/>
     </x:row>
     <x:row r="25" ht="64" customHeight="1">
       <x:c r="A25" s="6" t="str">
@@ -1005,6 +1107,10 @@
       <x:c r="G25" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H25" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I25" s="6" t="str"/>
     </x:row>
     <x:row r="26" ht="64" customHeight="1">
       <x:c r="A26" s="6" t="str">
@@ -1028,6 +1134,10 @@
       <x:c r="G26" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H26" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I26" s="6" t="str"/>
     </x:row>
     <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="6" t="str">
@@ -1051,6 +1161,10 @@
       <x:c r="G27" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H27" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I27" s="6" t="str"/>
     </x:row>
     <x:row r="28" ht="64" customHeight="1">
       <x:c r="A28" s="6" t="str">
@@ -1074,6 +1188,10 @@
       <x:c r="G28" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H28" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I28" s="6" t="str"/>
     </x:row>
     <x:row r="29" ht="64" customHeight="1">
       <x:c r="A29" s="6" t="str">
@@ -1097,6 +1215,10 @@
       <x:c r="G29" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H29" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I29" s="6" t="str"/>
     </x:row>
     <x:row r="30" ht="64" customHeight="1">
       <x:c r="A30" s="6" t="str">
@@ -1120,6 +1242,10 @@
       <x:c r="G30" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H30" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I30" s="6" t="str"/>
     </x:row>
     <x:row r="31" ht="64" customHeight="1">
       <x:c r="A31" s="6" t="str">
@@ -1143,6 +1269,10 @@
       <x:c r="G31" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H31" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I31" s="6" t="str"/>
     </x:row>
     <x:row r="32" ht="64" customHeight="1">
       <x:c r="A32" s="6" t="str">
@@ -1166,6 +1296,10 @@
       <x:c r="G32" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H32" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I32" s="6" t="str"/>
     </x:row>
     <x:row r="33" ht="64" customHeight="1">
       <x:c r="A33" s="6" t="str">
@@ -1189,6 +1323,10 @@
       <x:c r="G33" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H33" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I33" s="6" t="str"/>
     </x:row>
     <x:row r="34" ht="64" customHeight="1">
       <x:c r="A34" s="6" t="str">
@@ -1212,6 +1350,10 @@
       <x:c r="G34" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H34" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I34" s="6" t="str"/>
     </x:row>
     <x:row r="35" ht="64" customHeight="1">
       <x:c r="A35" s="6" t="str">
@@ -1235,11 +1377,15 @@
       <x:c r="G35" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H35" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I35" s="6" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea561d142d3f4601"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b6b7dffb61f4589"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10325,7 +10471,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58c09d9ff10744bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82476eb492c5439c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11417,7 +11563,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae7459f4e294cab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf65ac0efcdd64039"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12883,7 +13029,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2122b00a22054fd7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb70144793213466e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15894,7 +16040,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7887a1d285634422"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87eb23c39fc04910"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-ic.xlsx
+++ b/site/exports/hit-shenzhen-ic.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0f9f2f9058b8429c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rbccfebf6909b40df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rd10bf699e4fd4429"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Re6eff4c7f6294cf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R4b78f41e59284dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R109124c4f93347f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Re4e4be3e2e9848d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rd29cbbe2c53c4666"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rd8cf1f2172e94798"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R9af04595cd3c4e12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,8 +139,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T3_0" displayName="T3_0" ref="A1:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="9">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T3_0" displayName="T3_0" ref="A1:K35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
     <x:tableColumn id="3" name="院系"/>
@@ -150,14 +150,16 @@
     <x:tableColumn id="7" name="范围"/>
     <x:tableColumn id="8" name="主页可用性"/>
     <x:tableColumn id="9" name="替代官方职业报道（非个人主页）"/>
+    <x:tableColumn id="10" name="所属学校ID"/>
+    <x:tableColumn id="11" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T3_1" displayName="T3_1" ref="A1:Q235" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="17">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T3_1" displayName="T3_1" ref="A1:S235" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
     <x:tableColumn id="3" name="阶段/职位"/>
@@ -175,14 +177,16 @@
     <x:tableColumn id="15" name="备注及冲突"/>
     <x:tableColumn id="16" name="地域口径"/>
     <x:tableColumn id="17" name="来源"/>
+    <x:tableColumn id="18" name="所属学校ID"/>
+    <x:tableColumn id="19" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T3_2" displayName="T3_2" ref="A1:J34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T3_2" displayName="T3_2" ref="A1:L34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
     <x:tableColumn id="3" name="关系类型"/>
@@ -193,14 +197,16 @@
     <x:tableColumn id="8" name="已核在职主页"/>
     <x:tableColumn id="9" name="关系来源"/>
     <x:tableColumn id="10" name="任职来源"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T3_3" displayName="T3_3" ref="A1:J48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T3_3" displayName="T3_3" ref="A1:L48" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
     <x:tableColumn id="3" name="年份"/>
@@ -211,19 +217,23 @@
     <x:tableColumn id="8" name="作者归属依据"/>
     <x:tableColumn id="9" name="链接核验范围"/>
     <x:tableColumn id="10" name="备注"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T3_4" displayName="T3_4" ref="A1:E176" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="5">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T3_4" displayName="T3_4" ref="A1:G176" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
     <x:tableColumn id="3" name="链接"/>
     <x:tableColumn id="4" name="核验方式"/>
     <x:tableColumn id="5" name="查阅日期"/>
+    <x:tableColumn id="6" name="所属学校ID"/>
+    <x:tableColumn id="7" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -433,6 +443,8 @@
     <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -463,6 +475,12 @@
       <x:c r="I1" s="9" t="str">
         <x:v>替代官方职业报道（非个人主页）</x:v>
       </x:c>
+      <x:c r="J1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -490,6 +508,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -517,6 +541,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str"/>
+      <x:c r="J3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -544,6 +574,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I4" s="6" t="str"/>
+      <x:c r="J4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -571,6 +607,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I5" s="6" t="str"/>
+      <x:c r="J5" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -598,6 +640,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I6" s="6" t="str"/>
+      <x:c r="J6" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -625,6 +673,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I7" s="6" t="str"/>
+      <x:c r="J7" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -652,6 +706,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I8" s="6" t="str"/>
+      <x:c r="J8" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -679,6 +739,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -706,6 +772,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I10" s="6" t="str"/>
+      <x:c r="J10" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K10" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -733,6 +805,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I11" s="6" t="str"/>
+      <x:c r="J11" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K11" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -760,6 +838,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -787,6 +871,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K13" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -814,6 +904,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K14" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
       <x:c r="A15" s="6" t="str">
@@ -841,6 +937,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str"/>
+      <x:c r="J15" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K15" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="64" customHeight="1">
       <x:c r="A16" s="6" t="str">
@@ -868,6 +970,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I16" s="6" t="str"/>
+      <x:c r="J16" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K16" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="64" customHeight="1">
       <x:c r="A17" s="6" t="str">
@@ -895,6 +1003,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I17" s="6" t="str"/>
+      <x:c r="J17" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K17" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
       <x:c r="A18" s="6" t="str">
@@ -922,6 +1036,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I18" s="6" t="str"/>
+      <x:c r="J18" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K18" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="64" customHeight="1">
       <x:c r="A19" s="6" t="str">
@@ -949,6 +1069,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I19" s="6" t="str"/>
+      <x:c r="J19" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K19" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="64" customHeight="1">
       <x:c r="A20" s="6" t="str">
@@ -976,6 +1102,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I20" s="6" t="str"/>
+      <x:c r="J20" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K20" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="64" customHeight="1">
       <x:c r="A21" s="6" t="str">
@@ -1003,6 +1135,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I21" s="6" t="str"/>
+      <x:c r="J21" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K21" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="64" customHeight="1">
       <x:c r="A22" s="6" t="str">
@@ -1030,6 +1168,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I22" s="6" t="str"/>
+      <x:c r="J22" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K22" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="64" customHeight="1">
       <x:c r="A23" s="6" t="str">
@@ -1057,6 +1201,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I23" s="6" t="str"/>
+      <x:c r="J23" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K23" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="64" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -1084,6 +1234,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I24" s="6" t="str"/>
+      <x:c r="J24" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K24" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="64" customHeight="1">
       <x:c r="A25" s="6" t="str">
@@ -1111,6 +1267,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I25" s="6" t="str"/>
+      <x:c r="J25" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K25" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="64" customHeight="1">
       <x:c r="A26" s="6" t="str">
@@ -1138,6 +1300,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I26" s="6" t="str"/>
+      <x:c r="J26" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K26" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="6" t="str">
@@ -1165,6 +1333,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I27" s="6" t="str"/>
+      <x:c r="J27" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K27" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="64" customHeight="1">
       <x:c r="A28" s="6" t="str">
@@ -1192,6 +1366,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I28" s="6" t="str"/>
+      <x:c r="J28" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K28" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="64" customHeight="1">
       <x:c r="A29" s="6" t="str">
@@ -1219,6 +1399,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I29" s="6" t="str"/>
+      <x:c r="J29" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K29" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="64" customHeight="1">
       <x:c r="A30" s="6" t="str">
@@ -1246,6 +1432,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I30" s="6" t="str"/>
+      <x:c r="J30" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K30" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="64" customHeight="1">
       <x:c r="A31" s="6" t="str">
@@ -1273,6 +1465,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I31" s="6" t="str"/>
+      <x:c r="J31" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K31" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="64" customHeight="1">
       <x:c r="A32" s="6" t="str">
@@ -1300,6 +1498,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I32" s="6" t="str"/>
+      <x:c r="J32" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K32" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="64" customHeight="1">
       <x:c r="A33" s="6" t="str">
@@ -1327,6 +1531,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I33" s="6" t="str"/>
+      <x:c r="J33" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K33" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="64" customHeight="1">
       <x:c r="A34" s="6" t="str">
@@ -1354,6 +1564,12 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I34" s="6" t="str"/>
+      <x:c r="J34" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K34" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="64" customHeight="1">
       <x:c r="A35" s="6" t="str">
@@ -1381,11 +1597,17 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I35" s="6" t="str"/>
+      <x:c r="J35" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K35" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b6b7dffb61f4589"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d020de83df743f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1411,6 +1633,8 @@
     <x:col min="15" max="15" width="55" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="26" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="55" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="26" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -1465,6 +1689,12 @@
       <x:c r="Q1" s="9" t="str">
         <x:v>来源</x:v>
       </x:c>
+      <x:c r="R1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="S1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -1512,6 +1742,12 @@
       <x:c r="Q2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
       </x:c>
+      <x:c r="R2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -1558,6 +1794,12 @@
       </x:c>
       <x:c r="Q3" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
+      </x:c>
+      <x:c r="R3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
@@ -1592,6 +1834,12 @@
       <x:c r="Q4" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
       </x:c>
+      <x:c r="R4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -1625,6 +1873,12 @@
       <x:c r="Q5" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
       </x:c>
+      <x:c r="R5" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S5" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -1658,6 +1912,12 @@
       <x:c r="Q6" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
       </x:c>
+      <x:c r="R6" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S6" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -1690,6 +1950,12 @@
       <x:c r="P7" s="6" t="str"/>
       <x:c r="Q7" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
+      </x:c>
+      <x:c r="R7" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S7" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
@@ -1722,6 +1988,12 @@
       <x:c r="Q8" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
       </x:c>
+      <x:c r="R8" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S8" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -1767,6 +2039,12 @@
       <x:c r="Q9" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
       </x:c>
+      <x:c r="R9" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S9" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -1812,6 +2090,12 @@
       <x:c r="Q10" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
       </x:c>
+      <x:c r="R10" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S10" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -1856,6 +2140,12 @@
       </x:c>
       <x:c r="Q11" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
+      </x:c>
+      <x:c r="R11" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S11" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
@@ -1890,6 +2180,12 @@
       <x:c r="Q12" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
       </x:c>
+      <x:c r="R12" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S12" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -1923,6 +2219,12 @@
       <x:c r="Q13" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
       </x:c>
+      <x:c r="R13" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S13" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -1956,6 +2258,12 @@
       <x:c r="Q14" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
       </x:c>
+      <x:c r="R14" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S14" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
       <x:c r="A15" s="6" t="str">
@@ -1988,6 +2296,12 @@
       <x:c r="P15" s="6" t="str"/>
       <x:c r="Q15" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
+      </x:c>
+      <x:c r="R15" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S15" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="64" customHeight="1">
@@ -2020,6 +2334,12 @@
       <x:c r="Q16" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
       </x:c>
+      <x:c r="R16" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S16" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="64" customHeight="1">
       <x:c r="A17" s="6" t="str">
@@ -2053,6 +2373,12 @@
       <x:c r="Q17" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
       </x:c>
+      <x:c r="R17" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S17" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
       <x:c r="A18" s="6" t="str">
@@ -2086,6 +2412,12 @@
       <x:c r="Q18" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/limingyu</x:v>
       </x:c>
+      <x:c r="R18" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S18" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="64" customHeight="1">
       <x:c r="A19" s="6" t="str">
@@ -2133,6 +2465,12 @@
       <x:c r="Q19" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jihongjun</x:v>
       </x:c>
+      <x:c r="R19" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S19" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="64" customHeight="1">
       <x:c r="A20" s="6" t="str">
@@ -2180,6 +2518,12 @@
       <x:c r="Q20" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jihongjun</x:v>
       </x:c>
+      <x:c r="R20" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S20" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="64" customHeight="1">
       <x:c r="A21" s="6" t="str">
@@ -2226,6 +2570,12 @@
       </x:c>
       <x:c r="Q21" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jihongjun</x:v>
+      </x:c>
+      <x:c r="R21" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S21" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="64" customHeight="1">
@@ -2260,6 +2610,12 @@
       <x:c r="Q22" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jihongjun</x:v>
       </x:c>
+      <x:c r="R22" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S22" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="64" customHeight="1">
       <x:c r="A23" s="6" t="str">
@@ -2293,6 +2649,12 @@
       <x:c r="Q23" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jihongjun</x:v>
       </x:c>
+      <x:c r="R23" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S23" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="64" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -2325,6 +2687,12 @@
       <x:c r="P24" s="6" t="str"/>
       <x:c r="Q24" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jihongjun</x:v>
+      </x:c>
+      <x:c r="R24" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S24" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="64" customHeight="1">
@@ -2357,6 +2725,12 @@
       <x:c r="Q25" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jihongjun</x:v>
       </x:c>
+      <x:c r="R25" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S25" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="64" customHeight="1">
       <x:c r="A26" s="6" t="str">
@@ -2390,6 +2764,12 @@
       <x:c r="Q26" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jihongjun</x:v>
       </x:c>
+      <x:c r="R26" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S26" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="6" t="str">
@@ -2437,6 +2817,12 @@
       <x:c r="Q27" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/maxing</x:v>
       </x:c>
+      <x:c r="R27" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S27" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="64" customHeight="1">
       <x:c r="A28" s="6" t="str">
@@ -2484,6 +2870,12 @@
       <x:c r="Q28" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/maxing</x:v>
       </x:c>
+      <x:c r="R28" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S28" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="64" customHeight="1">
       <x:c r="A29" s="6" t="str">
@@ -2532,6 +2924,12 @@
       </x:c>
       <x:c r="Q29" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/maxing</x:v>
+      </x:c>
+      <x:c r="R29" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S29" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="64" customHeight="1">
@@ -2566,6 +2964,12 @@
       <x:c r="Q30" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/maxing</x:v>
       </x:c>
+      <x:c r="R30" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S30" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="64" customHeight="1">
       <x:c r="A31" s="6" t="str">
@@ -2599,6 +3003,12 @@
       <x:c r="Q31" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/maxing</x:v>
       </x:c>
+      <x:c r="R31" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S31" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="64" customHeight="1">
       <x:c r="A32" s="6" t="str">
@@ -2631,6 +3041,12 @@
       <x:c r="P32" s="6" t="str"/>
       <x:c r="Q32" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/maxing</x:v>
+      </x:c>
+      <x:c r="R32" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S32" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="64" customHeight="1">
@@ -2663,6 +3079,12 @@
       <x:c r="Q33" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/maxing</x:v>
       </x:c>
+      <x:c r="R33" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S33" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="64" customHeight="1">
       <x:c r="A34" s="6" t="str">
@@ -2710,6 +3132,12 @@
       <x:c r="Q34" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangmingjiang</x:v>
       </x:c>
+      <x:c r="R34" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S34" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="64" customHeight="1">
       <x:c r="A35" s="6" t="str">
@@ -2757,6 +3185,12 @@
       <x:c r="Q35" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangmingjiang</x:v>
       </x:c>
+      <x:c r="R35" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S35" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="64" customHeight="1">
       <x:c r="A36" s="6" t="str">
@@ -2803,6 +3237,12 @@
       </x:c>
       <x:c r="Q36" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangmingjiang</x:v>
+      </x:c>
+      <x:c r="R36" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S36" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="64" customHeight="1">
@@ -2836,6 +3276,12 @@
       <x:c r="P37" s="6" t="str"/>
       <x:c r="Q37" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangmingjiang</x:v>
+      </x:c>
+      <x:c r="R37" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S37" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="64" customHeight="1">
@@ -2870,6 +3316,12 @@
       <x:c r="Q38" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangmingjiang</x:v>
       </x:c>
+      <x:c r="R38" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S38" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="64" customHeight="1">
       <x:c r="A39" s="6" t="str">
@@ -2903,6 +3355,12 @@
       <x:c r="Q39" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangmingjiang</x:v>
       </x:c>
+      <x:c r="R39" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S39" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="64" customHeight="1">
       <x:c r="A40" s="6" t="str">
@@ -2936,6 +3394,12 @@
       <x:c r="Q40" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangmingjiang</x:v>
       </x:c>
+      <x:c r="R40" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S40" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="64" customHeight="1">
       <x:c r="A41" s="6" t="str">
@@ -2969,6 +3433,12 @@
       <x:c r="Q41" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangmingjiang</x:v>
       </x:c>
+      <x:c r="R41" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S41" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="64" customHeight="1">
       <x:c r="A42" s="6" t="str">
@@ -3014,6 +3484,12 @@
       <x:c r="Q42" s="6" t="str">
         <x:v>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aelm.202300674</x:v>
       </x:c>
+      <x:c r="R42" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S42" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="64" customHeight="1">
       <x:c r="A43" s="6" t="str">
@@ -3058,6 +3534,12 @@
       </x:c>
       <x:c r="Q43" s="6" t="str">
         <x:v>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aelm.202300674</x:v>
+      </x:c>
+      <x:c r="R43" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S43" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="64" customHeight="1">
@@ -3092,6 +3574,12 @@
       <x:c r="Q44" s="6" t="str">
         <x:v>https://par.nsf.gov/servlets/purl/10064529</x:v>
       </x:c>
+      <x:c r="R44" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S44" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="64" customHeight="1">
       <x:c r="A45" s="6" t="str">
@@ -3123,6 +3611,12 @@
       <x:c r="Q45" s="6" t="str">
         <x:v>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aelm.202300674</x:v>
       </x:c>
+      <x:c r="R45" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S45" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="64" customHeight="1">
       <x:c r="A46" s="6" t="str">
@@ -3156,6 +3650,12 @@
       <x:c r="Q46" s="6" t="str">
         <x:v>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aelm.202300674</x:v>
       </x:c>
+      <x:c r="R46" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S46" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="64" customHeight="1">
       <x:c r="A47" s="6" t="str">
@@ -3189,6 +3689,12 @@
       <x:c r="Q47" s="6" t="str">
         <x:v>https://advanced.onlinelibrary.wiley.com/doi/10.1002/aelm.202300674</x:v>
       </x:c>
+      <x:c r="R47" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S47" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="64" customHeight="1">
       <x:c r="A48" s="6" t="str">
@@ -3236,6 +3742,12 @@
       <x:c r="Q48" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qugeyang</x:v>
       </x:c>
+      <x:c r="R48" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S48" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="64" customHeight="1">
       <x:c r="A49" s="6" t="str">
@@ -3288,6 +3800,12 @@
       </x:c>
       <x:c r="Q49" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qugeyang</x:v>
+      </x:c>
+      <x:c r="R49" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S49" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="64" customHeight="1">
@@ -3322,6 +3840,12 @@
       <x:c r="Q50" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qugeyang</x:v>
       </x:c>
+      <x:c r="R50" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S50" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="64" customHeight="1">
       <x:c r="A51" s="6" t="str">
@@ -3354,6 +3878,12 @@
       <x:c r="P51" s="6" t="str"/>
       <x:c r="Q51" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qugeyang</x:v>
+      </x:c>
+      <x:c r="R51" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S51" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="64" customHeight="1">
@@ -3386,6 +3916,12 @@
       <x:c r="Q52" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qugeyang</x:v>
       </x:c>
+      <x:c r="R52" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S52" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="64" customHeight="1">
       <x:c r="A53" s="6" t="str">
@@ -3429,6 +3965,12 @@
       <x:c r="Q53" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jiangzhi</x:v>
       </x:c>
+      <x:c r="R53" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S53" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="64" customHeight="1">
       <x:c r="A54" s="6" t="str">
@@ -3472,6 +4014,12 @@
       <x:c r="Q54" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jiangzhi</x:v>
       </x:c>
+      <x:c r="R54" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S54" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="64" customHeight="1">
       <x:c r="A55" s="6" t="str">
@@ -3518,6 +4066,12 @@
       </x:c>
       <x:c r="Q55" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jiangzhi</x:v>
+      </x:c>
+      <x:c r="R55" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S55" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="64" customHeight="1">
@@ -3551,6 +4105,12 @@
       <x:c r="P56" s="6" t="str"/>
       <x:c r="Q56" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jiangzhi</x:v>
+      </x:c>
+      <x:c r="R56" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S56" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="64" customHeight="1">
@@ -3583,6 +4143,12 @@
       <x:c r="Q57" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jiangzhi</x:v>
       </x:c>
+      <x:c r="R57" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S57" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="64" customHeight="1">
       <x:c r="A58" s="6" t="str">
@@ -3630,6 +4196,12 @@
       <x:c r="Q58" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
       </x:c>
+      <x:c r="R58" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S58" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="64" customHeight="1">
       <x:c r="A59" s="6" t="str">
@@ -3677,6 +4249,12 @@
       <x:c r="Q59" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
       </x:c>
+      <x:c r="R59" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S59" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="64" customHeight="1">
       <x:c r="A60" s="6" t="str">
@@ -3724,6 +4302,12 @@
       <x:c r="Q60" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
       </x:c>
+      <x:c r="R60" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S60" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="64" customHeight="1">
       <x:c r="A61" s="6" t="str">
@@ -3770,6 +4354,12 @@
       </x:c>
       <x:c r="Q61" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
+      </x:c>
+      <x:c r="R61" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S61" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="64" customHeight="1">
@@ -3804,6 +4394,12 @@
       <x:c r="Q62" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
       </x:c>
+      <x:c r="R62" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S62" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="64" customHeight="1">
       <x:c r="A63" s="6" t="str">
@@ -3837,6 +4433,12 @@
       <x:c r="Q63" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
       </x:c>
+      <x:c r="R63" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S63" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="64" customHeight="1">
       <x:c r="A64" s="6" t="str">
@@ -3870,6 +4472,12 @@
       <x:c r="Q64" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
       </x:c>
+      <x:c r="R64" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S64" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="64" customHeight="1">
       <x:c r="A65" s="6" t="str">
@@ -3902,6 +4510,12 @@
       <x:c r="P65" s="6" t="str"/>
       <x:c r="Q65" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
+      </x:c>
+      <x:c r="R65" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S65" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="64" customHeight="1">
@@ -3934,6 +4548,12 @@
       <x:c r="Q66" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xiaojunjun</x:v>
       </x:c>
+      <x:c r="R66" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S66" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="64" customHeight="1">
       <x:c r="A67" s="6" t="str">
@@ -3983,6 +4603,12 @@
       <x:c r="Q67" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
       </x:c>
+      <x:c r="R67" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S67" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="64" customHeight="1">
       <x:c r="A68" s="6" t="str">
@@ -4031,6 +4657,12 @@
       </x:c>
       <x:c r="Q68" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
+      </x:c>
+      <x:c r="R68" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S68" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="64" customHeight="1">
@@ -4079,6 +4711,12 @@
       <x:c r="Q69" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
       </x:c>
+      <x:c r="R69" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S69" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="64" customHeight="1">
       <x:c r="A70" s="6" t="str">
@@ -4125,6 +4763,12 @@
       </x:c>
       <x:c r="Q70" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
+      </x:c>
+      <x:c r="R70" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S70" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="64" customHeight="1">
@@ -4159,6 +4803,12 @@
       <x:c r="Q71" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
       </x:c>
+      <x:c r="R71" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S71" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="64" customHeight="1">
       <x:c r="A72" s="6" t="str">
@@ -4192,6 +4842,12 @@
       <x:c r="Q72" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
       </x:c>
+      <x:c r="R72" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S72" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="64" customHeight="1">
       <x:c r="A73" s="6" t="str">
@@ -4225,6 +4881,12 @@
       <x:c r="Q73" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
       </x:c>
+      <x:c r="R73" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S73" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="64" customHeight="1">
       <x:c r="A74" s="6" t="str">
@@ -4258,6 +4920,12 @@
       <x:c r="Q74" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
       </x:c>
+      <x:c r="R74" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S74" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="64" customHeight="1">
       <x:c r="A75" s="6" t="str">
@@ -4290,6 +4958,12 @@
       <x:c r="P75" s="6" t="str"/>
       <x:c r="Q75" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
+      </x:c>
+      <x:c r="R75" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S75" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="64" customHeight="1">
@@ -4322,6 +4996,12 @@
       <x:c r="Q76" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
       </x:c>
+      <x:c r="R76" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S76" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="64" customHeight="1">
       <x:c r="A77" s="6" t="str">
@@ -4369,6 +5049,12 @@
       <x:c r="Q77" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenshumei</x:v>
       </x:c>
+      <x:c r="R77" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S77" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="64" customHeight="1">
       <x:c r="A78" s="6" t="str">
@@ -4421,6 +5107,12 @@
       </x:c>
       <x:c r="Q78" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenshumei</x:v>
+      </x:c>
+      <x:c r="R78" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S78" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="64" customHeight="1">
@@ -4455,6 +5147,12 @@
       <x:c r="Q79" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenshumei</x:v>
       </x:c>
+      <x:c r="R79" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S79" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="64" customHeight="1">
       <x:c r="A80" s="6" t="str">
@@ -4488,6 +5186,12 @@
       <x:c r="Q80" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenshumei</x:v>
       </x:c>
+      <x:c r="R80" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S80" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="64" customHeight="1">
       <x:c r="A81" s="6" t="str">
@@ -4521,6 +5225,12 @@
       <x:c r="Q81" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenshumei</x:v>
       </x:c>
+      <x:c r="R81" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S81" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="64" customHeight="1">
       <x:c r="A82" s="6" t="str">
@@ -4566,6 +5276,12 @@
       <x:c r="Q82" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenyimu</x:v>
       </x:c>
+      <x:c r="R82" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S82" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="64" customHeight="1">
       <x:c r="A83" s="6" t="str">
@@ -4612,6 +5328,12 @@
       </x:c>
       <x:c r="Q83" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenyimu</x:v>
+      </x:c>
+      <x:c r="R83" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S83" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="64" customHeight="1">
@@ -4644,6 +5366,12 @@
       <x:c r="Q84" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/chenyimu</x:v>
       </x:c>
+      <x:c r="R84" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S84" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="64" customHeight="1">
       <x:c r="A85" s="6" t="str">
@@ -4689,6 +5417,12 @@
       <x:c r="Q85" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/recgardening</x:v>
       </x:c>
+      <x:c r="R85" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S85" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="64" customHeight="1">
       <x:c r="A86" s="6" t="str">
@@ -4733,6 +5467,12 @@
       </x:c>
       <x:c r="Q86" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/recgardening</x:v>
+      </x:c>
+      <x:c r="R86" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S86" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="64" customHeight="1">
@@ -4766,6 +5506,12 @@
       <x:c r="P87" s="6" t="str"/>
       <x:c r="Q87" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/recgardening</x:v>
+      </x:c>
+      <x:c r="R87" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S87" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="64" customHeight="1">
@@ -4798,6 +5544,12 @@
       <x:c r="Q88" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/recgardening</x:v>
       </x:c>
+      <x:c r="R88" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S88" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="64" customHeight="1">
       <x:c r="A89" s="6" t="str">
@@ -4845,6 +5597,12 @@
       <x:c r="Q89" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhaoweiwei</x:v>
       </x:c>
+      <x:c r="R89" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S89" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="64" customHeight="1">
       <x:c r="A90" s="6" t="str">
@@ -4893,6 +5651,12 @@
       </x:c>
       <x:c r="Q90" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhaoweiwei</x:v>
+      </x:c>
+      <x:c r="R90" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S90" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="64" customHeight="1">
@@ -4927,6 +5691,12 @@
       <x:c r="Q91" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhaoweiwei</x:v>
       </x:c>
+      <x:c r="R91" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S91" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="92" ht="64" customHeight="1">
       <x:c r="A92" s="6" t="str">
@@ -4960,6 +5730,12 @@
       <x:c r="Q92" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhaoweiwei</x:v>
       </x:c>
+      <x:c r="R92" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S92" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" ht="64" customHeight="1">
       <x:c r="A93" s="6" t="str">
@@ -4992,6 +5768,12 @@
       <x:c r="P93" s="6" t="str"/>
       <x:c r="Q93" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhaoweiwei</x:v>
+      </x:c>
+      <x:c r="R93" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S93" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="64" customHeight="1">
@@ -5024,6 +5806,12 @@
       <x:c r="Q94" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhaoweiwei</x:v>
       </x:c>
+      <x:c r="R94" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S94" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="95" ht="64" customHeight="1">
       <x:c r="A95" s="6" t="str">
@@ -5071,6 +5859,12 @@
       <x:c r="Q95" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhongying</x:v>
       </x:c>
+      <x:c r="R95" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S95" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="96" ht="64" customHeight="1">
       <x:c r="A96" s="6" t="str">
@@ -5118,6 +5912,12 @@
       <x:c r="Q96" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhongying</x:v>
       </x:c>
+      <x:c r="R96" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S96" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="97" ht="64" customHeight="1">
       <x:c r="A97" s="6" t="str">
@@ -5165,6 +5965,12 @@
       <x:c r="Q97" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhongying</x:v>
       </x:c>
+      <x:c r="R97" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S97" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="98" ht="64" customHeight="1">
       <x:c r="A98" s="6" t="str">
@@ -5213,6 +6019,12 @@
       </x:c>
       <x:c r="Q98" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhongying</x:v>
+      </x:c>
+      <x:c r="R98" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S98" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="64" customHeight="1">
@@ -5247,6 +6059,12 @@
       <x:c r="Q99" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhongying</x:v>
       </x:c>
+      <x:c r="R99" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S99" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" ht="64" customHeight="1">
       <x:c r="A100" s="6" t="str">
@@ -5279,6 +6097,12 @@
       <x:c r="P100" s="6" t="str"/>
       <x:c r="Q100" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhongying</x:v>
+      </x:c>
+      <x:c r="R100" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S100" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="64" customHeight="1">
@@ -5311,6 +6135,12 @@
       <x:c r="Q101" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhongying</x:v>
       </x:c>
+      <x:c r="R101" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S101" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="64" customHeight="1">
       <x:c r="A102" s="6" t="str">
@@ -5358,6 +6188,12 @@
       <x:c r="Q102" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xuke</x:v>
       </x:c>
+      <x:c r="R102" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S102" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="64" customHeight="1">
       <x:c r="A103" s="6" t="str">
@@ -5405,6 +6241,12 @@
       <x:c r="Q103" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xuke</x:v>
       </x:c>
+      <x:c r="R103" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S103" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" ht="64" customHeight="1">
       <x:c r="A104" s="6" t="str">
@@ -5450,6 +6292,12 @@
       <x:c r="Q104" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xuke</x:v>
       </x:c>
+      <x:c r="R104" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S104" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="64" customHeight="1">
       <x:c r="A105" s="6" t="str">
@@ -5494,6 +6342,12 @@
       </x:c>
       <x:c r="Q105" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xuke</x:v>
+      </x:c>
+      <x:c r="R105" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S105" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="64" customHeight="1">
@@ -5528,6 +6382,12 @@
       <x:c r="Q106" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xuke</x:v>
       </x:c>
+      <x:c r="R106" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S106" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="64" customHeight="1">
       <x:c r="A107" s="6" t="str">
@@ -5560,6 +6420,12 @@
       <x:c r="P107" s="6" t="str"/>
       <x:c r="Q107" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xuke</x:v>
+      </x:c>
+      <x:c r="R107" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S107" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="64" customHeight="1">
@@ -5592,6 +6458,12 @@
       <x:c r="Q108" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xuke</x:v>
       </x:c>
+      <x:c r="R108" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S108" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" ht="64" customHeight="1">
       <x:c r="A109" s="6" t="str">
@@ -5627,6 +6499,12 @@
       <x:c r="Q109" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/xuke</x:v>
       </x:c>
+      <x:c r="R109" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S109" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" ht="64" customHeight="1">
       <x:c r="A110" s="6" t="str">
@@ -5674,6 +6552,12 @@
       <x:c r="Q110" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/huangcan</x:v>
       </x:c>
+      <x:c r="R110" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S110" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" ht="64" customHeight="1">
       <x:c r="A111" s="6" t="str">
@@ -5720,6 +6604,12 @@
       </x:c>
       <x:c r="Q111" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/huangcan</x:v>
+      </x:c>
+      <x:c r="R111" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S111" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="64" customHeight="1">
@@ -5753,6 +6643,12 @@
       <x:c r="P112" s="6" t="str"/>
       <x:c r="Q112" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/huangcan</x:v>
+      </x:c>
+      <x:c r="R112" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S112" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="64" customHeight="1">
@@ -5785,6 +6681,12 @@
       <x:c r="Q113" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/huangcan</x:v>
       </x:c>
+      <x:c r="R113" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S113" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="114" ht="64" customHeight="1">
       <x:c r="A114" s="6" t="str">
@@ -5830,6 +6732,12 @@
       <x:c r="Q114" s="6" t="str">
         <x:v>https://ncmte.nimte.ac.cn/view-2305.html</x:v>
       </x:c>
+      <x:c r="R114" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S114" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" ht="64" customHeight="1">
       <x:c r="A115" s="6" t="str">
@@ -5877,6 +6785,12 @@
       <x:c r="Q115" s="6" t="str">
         <x:v>https://ncmte.nimte.ac.cn/view-2305.html</x:v>
       </x:c>
+      <x:c r="R115" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S115" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" ht="64" customHeight="1">
       <x:c r="A116" s="6" t="str">
@@ -5921,6 +6835,12 @@
       </x:c>
       <x:c r="Q116" s="6" t="str">
         <x:v>https://ncmte.nimte.ac.cn/view-2305.html</x:v>
+      </x:c>
+      <x:c r="R116" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S116" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="64" customHeight="1">
@@ -5962,6 +6882,12 @@
       </x:c>
       <x:c r="Q117" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/daimingzhihit</x:v>
+      </x:c>
+      <x:c r="R117" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S117" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="64" customHeight="1">
@@ -5997,6 +6923,12 @@
       <x:c r="P118" s="6" t="str"/>
       <x:c r="Q118" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/daimingzhihit</x:v>
+      </x:c>
+      <x:c r="R118" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S118" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="64" customHeight="1">
@@ -6029,6 +6961,12 @@
       <x:c r="Q119" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/daimingzhihit</x:v>
       </x:c>
+      <x:c r="R119" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S119" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" ht="64" customHeight="1">
       <x:c r="A120" s="6" t="str">
@@ -6075,6 +7013,12 @@
       </x:c>
       <x:c r="Q120" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangjiawei</x:v>
+      </x:c>
+      <x:c r="R120" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S120" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="64" customHeight="1">
@@ -6122,6 +7066,12 @@
       </x:c>
       <x:c r="Q121" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangjiawei</x:v>
+      </x:c>
+      <x:c r="R121" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S121" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="64" customHeight="1">
@@ -6156,6 +7106,12 @@
       <x:c r="Q122" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangjiawei</x:v>
       </x:c>
+      <x:c r="R122" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S122" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="123" ht="64" customHeight="1">
       <x:c r="A123" s="6" t="str">
@@ -6189,6 +7145,12 @@
       <x:c r="Q123" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangjiawei</x:v>
       </x:c>
+      <x:c r="R123" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S123" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="124" ht="64" customHeight="1">
       <x:c r="A124" s="6" t="str">
@@ -6221,6 +7183,12 @@
       <x:c r="P124" s="6" t="str"/>
       <x:c r="Q124" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangjiawei</x:v>
+      </x:c>
+      <x:c r="R124" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S124" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="64" customHeight="1">
@@ -6253,6 +7221,12 @@
       <x:c r="Q125" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangjiawei</x:v>
       </x:c>
+      <x:c r="R125" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S125" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="64" customHeight="1">
       <x:c r="A126" s="6" t="str">
@@ -6301,6 +7275,12 @@
       </x:c>
       <x:c r="Q126" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangyongjie</x:v>
+      </x:c>
+      <x:c r="R126" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S126" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="64" customHeight="1">
@@ -6349,6 +7329,12 @@
       <x:c r="Q127" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangyongjie</x:v>
       </x:c>
+      <x:c r="R127" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S127" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="128" ht="64" customHeight="1">
       <x:c r="A128" s="6" t="str">
@@ -6397,6 +7383,12 @@
       </x:c>
       <x:c r="Q128" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangyongjie</x:v>
+      </x:c>
+      <x:c r="R128" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S128" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="64" customHeight="1">
@@ -6431,6 +7423,12 @@
       <x:c r="Q129" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangyongjie</x:v>
       </x:c>
+      <x:c r="R129" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S129" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="64" customHeight="1">
       <x:c r="A130" s="6" t="str">
@@ -6464,6 +7462,12 @@
       <x:c r="Q130" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangyongjie</x:v>
       </x:c>
+      <x:c r="R130" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S130" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" ht="64" customHeight="1">
       <x:c r="A131" s="6" t="str">
@@ -6496,6 +7500,12 @@
       <x:c r="P131" s="6" t="str"/>
       <x:c r="Q131" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangyongjie</x:v>
+      </x:c>
+      <x:c r="R131" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S131" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="64" customHeight="1">
@@ -6528,6 +7538,12 @@
       <x:c r="Q132" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangyongjie</x:v>
       </x:c>
+      <x:c r="R132" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S132" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="133" ht="64" customHeight="1">
       <x:c r="A133" s="6" t="str">
@@ -6575,6 +7591,12 @@
       <x:c r="Q133" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jindongdong</x:v>
       </x:c>
+      <x:c r="R133" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S133" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="134" ht="64" customHeight="1">
       <x:c r="A134" s="6" t="str">
@@ -6622,6 +7644,12 @@
       <x:c r="Q134" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jindongdong</x:v>
       </x:c>
+      <x:c r="R134" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S134" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="135" ht="64" customHeight="1">
       <x:c r="A135" s="6" t="str">
@@ -6668,6 +7696,12 @@
       </x:c>
       <x:c r="Q135" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jindongdong</x:v>
+      </x:c>
+      <x:c r="R135" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S135" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="64" customHeight="1">
@@ -6702,6 +7736,12 @@
       <x:c r="Q136" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jindongdong</x:v>
       </x:c>
+      <x:c r="R136" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S136" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" ht="64" customHeight="1">
       <x:c r="A137" s="6" t="str">
@@ -6734,6 +7774,12 @@
       <x:c r="P137" s="6" t="str"/>
       <x:c r="Q137" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jindongdong</x:v>
+      </x:c>
+      <x:c r="R137" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S137" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="64" customHeight="1">
@@ -6766,6 +7812,12 @@
       <x:c r="Q138" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/jindongdong</x:v>
       </x:c>
+      <x:c r="R138" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S138" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="139" ht="64" customHeight="1">
       <x:c r="A139" s="6" t="str">
@@ -6813,6 +7865,12 @@
       <x:c r="Q139" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/hujingtian</x:v>
       </x:c>
+      <x:c r="R139" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S139" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="140" ht="64" customHeight="1">
       <x:c r="A140" s="6" t="str">
@@ -6859,6 +7917,12 @@
       </x:c>
       <x:c r="Q140" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/hujingtian</x:v>
+      </x:c>
+      <x:c r="R140" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S140" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="64" customHeight="1">
@@ -6894,6 +7958,12 @@
       <x:c r="P141" s="6" t="str"/>
       <x:c r="Q141" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/hujingtian</x:v>
+      </x:c>
+      <x:c r="R141" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S141" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="64" customHeight="1">
@@ -6927,6 +7997,12 @@
       <x:c r="P142" s="6" t="str"/>
       <x:c r="Q142" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/hujingtian</x:v>
+      </x:c>
+      <x:c r="R142" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S142" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="64" customHeight="1">
@@ -6957,6 +8033,12 @@
       <x:c r="Q143" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/hujingtian</x:v>
       </x:c>
+      <x:c r="R143" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S143" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="144" ht="64" customHeight="1">
       <x:c r="A144" s="6" t="str">
@@ -7004,6 +8086,12 @@
       <x:c r="Q144" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
       </x:c>
+      <x:c r="R144" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S144" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="145" ht="64" customHeight="1">
       <x:c r="A145" s="6" t="str">
@@ -7051,6 +8139,12 @@
       <x:c r="Q145" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
       </x:c>
+      <x:c r="R145" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S145" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="146" ht="64" customHeight="1">
       <x:c r="A146" s="6" t="str">
@@ -7098,6 +8192,12 @@
       <x:c r="Q146" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
       </x:c>
+      <x:c r="R146" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S146" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="147" ht="64" customHeight="1">
       <x:c r="A147" s="6" t="str">
@@ -7146,6 +8246,12 @@
       </x:c>
       <x:c r="Q147" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
+      </x:c>
+      <x:c r="R147" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S147" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="64" customHeight="1">
@@ -7180,6 +8286,12 @@
       <x:c r="Q148" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
       </x:c>
+      <x:c r="R148" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S148" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="149" ht="64" customHeight="1">
       <x:c r="A149" s="6" t="str">
@@ -7213,6 +8325,12 @@
       <x:c r="Q149" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
       </x:c>
+      <x:c r="R149" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S149" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" ht="64" customHeight="1">
       <x:c r="A150" s="6" t="str">
@@ -7246,6 +8364,12 @@
       <x:c r="Q150" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
       </x:c>
+      <x:c r="R150" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S150" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="151" ht="64" customHeight="1">
       <x:c r="A151" s="6" t="str">
@@ -7279,6 +8403,12 @@
       <x:c r="Q151" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
       </x:c>
+      <x:c r="R151" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S151" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="152" ht="64" customHeight="1">
       <x:c r="A152" s="6" t="str">
@@ -7311,6 +8441,12 @@
       <x:c r="P152" s="6" t="str"/>
       <x:c r="Q152" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
+      </x:c>
+      <x:c r="R152" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S152" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="64" customHeight="1">
@@ -7343,6 +8479,12 @@
       <x:c r="Q153" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/qinjingkai</x:v>
       </x:c>
+      <x:c r="R153" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S153" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="154" ht="64" customHeight="1">
       <x:c r="A154" s="6" t="str">
@@ -7391,6 +8533,12 @@
       </x:c>
       <x:c r="Q154" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/cuiaijiao</x:v>
+      </x:c>
+      <x:c r="R154" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S154" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="64" customHeight="1">
@@ -7439,6 +8587,12 @@
       <x:c r="Q155" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/cuiaijiao</x:v>
       </x:c>
+      <x:c r="R155" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S155" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="156" ht="64" customHeight="1">
       <x:c r="A156" s="6" t="str">
@@ -7487,6 +8641,12 @@
       </x:c>
       <x:c r="Q156" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/cuiaijiao</x:v>
+      </x:c>
+      <x:c r="R156" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S156" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="64" customHeight="1">
@@ -7521,6 +8681,12 @@
       <x:c r="Q157" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/cuiaijiao</x:v>
       </x:c>
+      <x:c r="R157" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S157" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="158" ht="64" customHeight="1">
       <x:c r="A158" s="6" t="str">
@@ -7554,6 +8720,12 @@
       <x:c r="Q158" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/cuiaijiao</x:v>
       </x:c>
+      <x:c r="R158" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S158" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="159" ht="64" customHeight="1">
       <x:c r="A159" s="6" t="str">
@@ -7587,6 +8759,12 @@
       <x:c r="Q159" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/cuiaijiao</x:v>
       </x:c>
+      <x:c r="R159" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S159" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="160" ht="64" customHeight="1">
       <x:c r="A160" s="6" t="str">
@@ -7619,6 +8797,12 @@
       <x:c r="P160" s="6" t="str"/>
       <x:c r="Q160" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/cuiaijiao</x:v>
+      </x:c>
+      <x:c r="R160" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S160" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="64" customHeight="1">
@@ -7651,6 +8835,12 @@
       <x:c r="Q161" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/cuiaijiao</x:v>
       </x:c>
+      <x:c r="R161" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S161" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="162" ht="64" customHeight="1">
       <x:c r="A162" s="6" t="str">
@@ -7699,6 +8889,12 @@
       </x:c>
       <x:c r="Q162" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangfeihit</x:v>
+      </x:c>
+      <x:c r="R162" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S162" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="64" customHeight="1">
@@ -7747,6 +8943,12 @@
       <x:c r="Q163" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangfeihit</x:v>
       </x:c>
+      <x:c r="R163" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S163" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="164" ht="64" customHeight="1">
       <x:c r="A164" s="6" t="str">
@@ -7794,6 +8996,12 @@
       <x:c r="Q164" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangfeihit</x:v>
       </x:c>
+      <x:c r="R164" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S164" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="165" ht="64" customHeight="1">
       <x:c r="A165" s="6" t="str">
@@ -7838,6 +9046,12 @@
       </x:c>
       <x:c r="Q165" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangfeihit</x:v>
+      </x:c>
+      <x:c r="R165" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S165" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="64" customHeight="1">
@@ -7872,6 +9086,12 @@
       <x:c r="Q166" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangfeihit</x:v>
       </x:c>
+      <x:c r="R166" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S166" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="167" ht="64" customHeight="1">
       <x:c r="A167" s="6" t="str">
@@ -7904,6 +9124,12 @@
       <x:c r="P167" s="6" t="str"/>
       <x:c r="Q167" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangfeihit</x:v>
+      </x:c>
+      <x:c r="R167" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S167" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="64" customHeight="1">
@@ -7936,6 +9162,12 @@
       <x:c r="Q168" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/wangfeihit</x:v>
       </x:c>
+      <x:c r="R168" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S168" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="169" ht="64" customHeight="1">
       <x:c r="A169" s="6" t="str">
@@ -7983,6 +9215,12 @@
       <x:c r="Q169" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/KaiyangWang</x:v>
       </x:c>
+      <x:c r="R169" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S169" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="170" ht="64" customHeight="1">
       <x:c r="A170" s="6" t="str">
@@ -8030,6 +9268,12 @@
       <x:c r="Q170" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/KaiyangWang</x:v>
       </x:c>
+      <x:c r="R170" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S170" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="171" ht="64" customHeight="1">
       <x:c r="A171" s="6" t="str">
@@ -8076,6 +9320,12 @@
       </x:c>
       <x:c r="Q171" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/KaiyangWang</x:v>
+      </x:c>
+      <x:c r="R171" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S171" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="64" customHeight="1">
@@ -8110,6 +9360,12 @@
       <x:c r="Q172" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/KaiyangWang</x:v>
       </x:c>
+      <x:c r="R172" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S172" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="173" ht="64" customHeight="1">
       <x:c r="A173" s="6" t="str">
@@ -8143,6 +9399,12 @@
       <x:c r="Q173" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/KaiyangWang</x:v>
       </x:c>
+      <x:c r="R173" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S173" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="174" ht="64" customHeight="1">
       <x:c r="A174" s="6" t="str">
@@ -8176,6 +9438,12 @@
       <x:c r="Q174" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/KaiyangWang</x:v>
       </x:c>
+      <x:c r="R174" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S174" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="175" ht="64" customHeight="1">
       <x:c r="A175" s="6" t="str">
@@ -8208,6 +9476,12 @@
       <x:c r="P175" s="6" t="str"/>
       <x:c r="Q175" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/KaiyangWang</x:v>
+      </x:c>
+      <x:c r="R175" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S175" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="64" customHeight="1">
@@ -8240,6 +9514,12 @@
       <x:c r="Q176" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/KaiyangWang</x:v>
       </x:c>
+      <x:c r="R176" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S176" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="177" ht="64" customHeight="1">
       <x:c r="A177" s="6" t="str">
@@ -8283,6 +9563,12 @@
       <x:c r="Q177" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/ruanqifeng</x:v>
       </x:c>
+      <x:c r="R177" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S177" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="178" ht="64" customHeight="1">
       <x:c r="A178" s="6" t="str">
@@ -8325,6 +9611,12 @@
       </x:c>
       <x:c r="Q178" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/ruanqifeng</x:v>
+      </x:c>
+      <x:c r="R178" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S178" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="64" customHeight="1">
@@ -8355,6 +9647,12 @@
       <x:c r="Q179" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/ruanqifeng</x:v>
       </x:c>
+      <x:c r="R179" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S179" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="180" ht="64" customHeight="1">
       <x:c r="A180" s="6" t="str">
@@ -8386,6 +9684,12 @@
       <x:c r="Q180" s="6" t="str">
         <x:v>https://www.phy.cuhk.edu.hk/~jfwang/HTML/people.htm</x:v>
       </x:c>
+      <x:c r="R180" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S180" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="181" ht="64" customHeight="1">
       <x:c r="A181" s="6" t="str">
@@ -8435,6 +9739,12 @@
       <x:c r="Q181" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liyufeng</x:v>
       </x:c>
+      <x:c r="R181" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S181" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="182" ht="64" customHeight="1">
       <x:c r="A182" s="6" t="str">
@@ -8484,6 +9794,12 @@
       <x:c r="Q182" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liyufeng</x:v>
       </x:c>
+      <x:c r="R182" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S182" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="183" ht="64" customHeight="1">
       <x:c r="A183" s="6" t="str">
@@ -8530,6 +9846,12 @@
       </x:c>
       <x:c r="Q183" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liyufeng</x:v>
+      </x:c>
+      <x:c r="R183" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S183" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="64" customHeight="1">
@@ -8564,6 +9886,12 @@
       <x:c r="Q184" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liyufeng</x:v>
       </x:c>
+      <x:c r="R184" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S184" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="185" ht="64" customHeight="1">
       <x:c r="A185" s="6" t="str">
@@ -8597,6 +9925,12 @@
       <x:c r="Q185" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liyufeng</x:v>
       </x:c>
+      <x:c r="R185" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S185" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="186" ht="64" customHeight="1">
       <x:c r="A186" s="6" t="str">
@@ -8630,6 +9964,12 @@
       <x:c r="Q186" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liyufeng</x:v>
       </x:c>
+      <x:c r="R186" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S186" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="187" ht="64" customHeight="1">
       <x:c r="A187" s="6" t="str">
@@ -8662,6 +10002,12 @@
       <x:c r="P187" s="6" t="str"/>
       <x:c r="Q187" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liyufeng</x:v>
+      </x:c>
+      <x:c r="R187" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S187" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="64" customHeight="1">
@@ -8694,6 +10040,12 @@
       <x:c r="Q188" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liyufeng</x:v>
       </x:c>
+      <x:c r="R188" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S188" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="189" ht="64" customHeight="1">
       <x:c r="A189" s="6" t="str">
@@ -8741,6 +10093,12 @@
       <x:c r="Q189" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
       </x:c>
+      <x:c r="R189" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S189" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="190" ht="64" customHeight="1">
       <x:c r="A190" s="6" t="str">
@@ -8787,6 +10145,12 @@
       </x:c>
       <x:c r="Q190" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
+      </x:c>
+      <x:c r="R190" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S190" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="64" customHeight="1">
@@ -8821,6 +10185,12 @@
       <x:c r="Q191" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
       </x:c>
+      <x:c r="R191" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S191" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="192" ht="64" customHeight="1">
       <x:c r="A192" s="6" t="str">
@@ -8854,6 +10224,12 @@
       <x:c r="Q192" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
       </x:c>
+      <x:c r="R192" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S192" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="193" ht="64" customHeight="1">
       <x:c r="A193" s="6" t="str">
@@ -8887,6 +10263,12 @@
       <x:c r="Q193" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
       </x:c>
+      <x:c r="R193" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S193" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="194" ht="64" customHeight="1">
       <x:c r="A194" s="6" t="str">
@@ -8919,6 +10301,12 @@
       <x:c r="P194" s="6" t="str"/>
       <x:c r="Q194" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
+      </x:c>
+      <x:c r="R194" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S194" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="64" customHeight="1">
@@ -8951,6 +10339,12 @@
       <x:c r="Q195" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
       </x:c>
+      <x:c r="R195" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S195" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="196" ht="64" customHeight="1">
       <x:c r="A196" s="6" t="str">
@@ -8986,6 +10380,12 @@
       <x:c r="Q196" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhangmingyu</x:v>
       </x:c>
+      <x:c r="R196" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S196" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="197" ht="64" customHeight="1">
       <x:c r="A197" s="6" t="str">
@@ -9035,6 +10435,12 @@
       <x:c r="Q197" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
+      <x:c r="R197" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S197" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="198" ht="64" customHeight="1">
       <x:c r="A198" s="6" t="str">
@@ -9084,6 +10490,12 @@
       <x:c r="Q198" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
+      <x:c r="R198" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S198" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="199" ht="64" customHeight="1">
       <x:c r="A199" s="6" t="str">
@@ -9132,6 +10544,12 @@
       </x:c>
       <x:c r="Q199" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
+      </x:c>
+      <x:c r="R199" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S199" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="64" customHeight="1">
@@ -9164,6 +10582,12 @@
       <x:c r="Q200" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/WenjunChen</x:v>
       </x:c>
+      <x:c r="R200" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S200" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="201" ht="64" customHeight="1">
       <x:c r="A201" s="6" t="str">
@@ -9195,6 +10619,12 @@
       <x:c r="Q201" s="6" t="str">
         <x:v>https://ic.hitsz.edu.cn/szll/qzjs/fjs.htm</x:v>
       </x:c>
+      <x:c r="R201" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S201" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="202" ht="64" customHeight="1">
       <x:c r="A202" s="6" t="str">
@@ -9228,6 +10658,12 @@
       <x:c r="Q202" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
+      <x:c r="R202" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S202" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="203" ht="64" customHeight="1">
       <x:c r="A203" s="6" t="str">
@@ -9263,6 +10699,12 @@
       <x:c r="Q203" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
+      <x:c r="R203" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S203" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="204" ht="64" customHeight="1">
       <x:c r="A204" s="6" t="str">
@@ -9298,6 +10740,12 @@
       <x:c r="Q204" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
+      <x:c r="R204" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S204" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="205" ht="64" customHeight="1">
       <x:c r="A205" s="6" t="str">
@@ -9332,6 +10780,12 @@
       <x:c r="P205" s="6" t="str"/>
       <x:c r="Q205" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
+      </x:c>
+      <x:c r="R205" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S205" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="64" customHeight="1">
@@ -9366,6 +10820,12 @@
       <x:c r="Q206" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
+      <x:c r="R206" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S206" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="207" ht="64" customHeight="1">
       <x:c r="A207" s="6" t="str">
@@ -9401,6 +10861,12 @@
       <x:c r="Q207" s="6" t="str">
         <x:v>https://escholarship.org/content/qt3gm80490/qt3gm80490.pdf</x:v>
       </x:c>
+      <x:c r="R207" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S207" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="208" ht="64" customHeight="1">
       <x:c r="A208" s="6" t="str">
@@ -9448,6 +10914,12 @@
       <x:c r="Q208" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
       </x:c>
+      <x:c r="R208" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S208" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="209" ht="64" customHeight="1">
       <x:c r="A209" s="6" t="str">
@@ -9495,6 +10967,12 @@
       <x:c r="Q209" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
       </x:c>
+      <x:c r="R209" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S209" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="210" ht="64" customHeight="1">
       <x:c r="A210" s="6" t="str">
@@ -9541,6 +11019,12 @@
       </x:c>
       <x:c r="Q210" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
+      </x:c>
+      <x:c r="R210" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S210" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="64" customHeight="1">
@@ -9575,6 +11059,12 @@
       <x:c r="Q211" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
       </x:c>
+      <x:c r="R211" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S211" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="212" ht="64" customHeight="1">
       <x:c r="A212" s="6" t="str">
@@ -9608,6 +11098,12 @@
       <x:c r="Q212" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
       </x:c>
+      <x:c r="R212" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S212" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="213" ht="64" customHeight="1">
       <x:c r="A213" s="6" t="str">
@@ -9641,6 +11137,12 @@
       <x:c r="Q213" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
       </x:c>
+      <x:c r="R213" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S213" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="214" ht="64" customHeight="1">
       <x:c r="A214" s="6" t="str">
@@ -9673,6 +11175,12 @@
       <x:c r="P214" s="6" t="str"/>
       <x:c r="Q214" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
+      </x:c>
+      <x:c r="R214" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S214" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="64" customHeight="1">
@@ -9705,6 +11213,12 @@
       <x:c r="Q215" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/zhuwenbo</x:v>
       </x:c>
+      <x:c r="R215" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S215" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="216" ht="64" customHeight="1">
       <x:c r="A216" s="6" t="str">
@@ -9750,6 +11264,12 @@
       <x:c r="Q216" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
       </x:c>
+      <x:c r="R216" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S216" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="217" ht="64" customHeight="1">
       <x:c r="A217" s="6" t="str">
@@ -9795,6 +11315,12 @@
       <x:c r="Q217" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
       </x:c>
+      <x:c r="R217" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S217" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="218" ht="64" customHeight="1">
       <x:c r="A218" s="6" t="str">
@@ -9839,6 +11365,12 @@
       </x:c>
       <x:c r="Q218" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
+      </x:c>
+      <x:c r="R218" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S218" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="64" customHeight="1">
@@ -9873,6 +11405,12 @@
       <x:c r="Q219" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
       </x:c>
+      <x:c r="R219" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S219" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" ht="64" customHeight="1">
       <x:c r="A220" s="6" t="str">
@@ -9906,6 +11444,12 @@
       <x:c r="Q220" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
       </x:c>
+      <x:c r="R220" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S220" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" ht="64" customHeight="1">
       <x:c r="A221" s="6" t="str">
@@ -9939,6 +11483,12 @@
       <x:c r="Q221" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
       </x:c>
+      <x:c r="R221" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S221" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="222" ht="64" customHeight="1">
       <x:c r="A222" s="6" t="str">
@@ -9971,6 +11521,12 @@
       <x:c r="P222" s="6" t="str"/>
       <x:c r="Q222" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
+      </x:c>
+      <x:c r="R222" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S222" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="64" customHeight="1">
@@ -10003,6 +11559,12 @@
       <x:c r="Q223" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/liufeihua</x:v>
       </x:c>
+      <x:c r="R223" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S223" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="224" ht="64" customHeight="1">
       <x:c r="A224" s="6" t="str">
@@ -10048,6 +11610,12 @@
       <x:c r="Q224" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/likang</x:v>
       </x:c>
+      <x:c r="R224" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S224" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="225" ht="64" customHeight="1">
       <x:c r="A225" s="6" t="str">
@@ -10094,6 +11662,12 @@
       </x:c>
       <x:c r="Q225" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/likang</x:v>
+      </x:c>
+      <x:c r="R225" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S225" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="64" customHeight="1">
@@ -10128,6 +11702,12 @@
       <x:c r="Q226" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/likang</x:v>
       </x:c>
+      <x:c r="R226" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S226" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="227" ht="64" customHeight="1">
       <x:c r="A227" s="6" t="str">
@@ -10161,6 +11741,12 @@
       <x:c r="Q227" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/likang</x:v>
       </x:c>
+      <x:c r="R227" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S227" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="228" ht="64" customHeight="1">
       <x:c r="A228" s="6" t="str">
@@ -10192,6 +11778,12 @@
       <x:c r="Q228" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/likang</x:v>
       </x:c>
+      <x:c r="R228" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S228" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="229" ht="64" customHeight="1">
       <x:c r="A229" s="6" t="str">
@@ -10239,6 +11831,12 @@
       <x:c r="Q229" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
       </x:c>
+      <x:c r="R229" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S229" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="230" ht="64" customHeight="1">
       <x:c r="A230" s="6" t="str">
@@ -10286,6 +11884,12 @@
       <x:c r="Q230" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
       </x:c>
+      <x:c r="R230" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S230" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="231" ht="64" customHeight="1">
       <x:c r="A231" s="6" t="str">
@@ -10336,6 +11940,12 @@
       </x:c>
       <x:c r="Q231" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
+      </x:c>
+      <x:c r="R231" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S231" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="64" customHeight="1">
@@ -10370,6 +11980,12 @@
       <x:c r="Q232" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
       </x:c>
+      <x:c r="R232" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S232" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="233" ht="64" customHeight="1">
       <x:c r="A233" s="6" t="str">
@@ -10403,6 +12019,12 @@
       <x:c r="Q233" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
       </x:c>
+      <x:c r="R233" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S233" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="234" ht="64" customHeight="1">
       <x:c r="A234" s="6" t="str">
@@ -10435,6 +12057,12 @@
       <x:c r="P234" s="6" t="str"/>
       <x:c r="Q234" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
+      </x:c>
+      <x:c r="R234" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S234" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="64" customHeight="1">
@@ -10467,11 +12095,17 @@
       <x:c r="Q235" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/fenghuanhuan</x:v>
       </x:c>
+      <x:c r="R235" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S235" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82476eb492c5439c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf50c55d73ef498b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10490,6 +12124,8 @@
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="55" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -10523,6 +12159,12 @@
       <x:c r="J1" s="9" t="str">
         <x:v>任职来源</x:v>
       </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="L1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -10555,6 +12197,12 @@
       <x:c r="J2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
       </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -10585,6 +12233,12 @@
       <x:c r="J3" s="6" t="str">
         <x:v>https://www.pcl.ac.cn/html/999/2026-07-06/content-4718.html</x:v>
       </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -10617,6 +12271,12 @@
       <x:c r="J4" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/tinatian</x:v>
       </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -10649,6 +12309,12 @@
       <x:c r="J5" s="6" t="str">
         <x:v>https://www.ee.t.u-tokyo.ac.jp/en/staff/someya-takao/</x:v>
       </x:c>
+      <x:c r="K5" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -10681,6 +12347,12 @@
       <x:c r="J6" s="6" t="str">
         <x:v>https://www3.ntu.edu.sg/home/CHENXD/PI.html</x:v>
       </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -10709,6 +12381,12 @@
         <x:v>https://homepage.hit.edu.cn/chenhongtao</x:v>
       </x:c>
       <x:c r="J7" s="6" t="str"/>
+      <x:c r="K7" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L7" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -10739,6 +12417,12 @@
       <x:c r="J8" s="6" t="str">
         <x:v>https://physics.hkbu.edu.hk/people/faculty-members</x:v>
       </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L8" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -10771,6 +12455,12 @@
       <x:c r="J9" s="6" t="str">
         <x:v>https://med.stanford.edu/profiles/sheng-xu</x:v>
       </x:c>
+      <x:c r="K9" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L9" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -10803,6 +12493,12 @@
       <x:c r="J10" s="6" t="str">
         <x:v>https://www.ntu.edu.sg/eee/faculty</x:v>
       </x:c>
+      <x:c r="K10" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L10" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -10835,6 +12531,12 @@
       <x:c r="J11" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/yanjiuchun?lang=zh</x:v>
       </x:c>
+      <x:c r="K11" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L11" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -10865,6 +12567,12 @@
       <x:c r="J12" s="6" t="str">
         <x:v>https://facultyaffairs.psu.edu/atherton-professors/</x:v>
       </x:c>
+      <x:c r="K12" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L12" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -10897,6 +12605,12 @@
       <x:c r="J13" s="6" t="str">
         <x:v>https://www.sustech.edu.cn/zh/leadership/xueqikun.html</x:v>
       </x:c>
+      <x:c r="K13" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L13" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -10929,6 +12643,12 @@
       <x:c r="J14" s="6" t="str">
         <x:v>https://www.phys.tsinghua.edu.cn/info/1099/4230.htm</x:v>
       </x:c>
+      <x:c r="K14" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L14" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
       <x:c r="A15" s="6" t="str">
@@ -10961,6 +12681,12 @@
       <x:c r="J15" s="6" t="str">
         <x:v>https://matsci.ucsd.edu/faculty/yu-qiao</x:v>
       </x:c>
+      <x:c r="K15" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L15" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="64" customHeight="1">
       <x:c r="A16" s="6" t="str">
@@ -10993,6 +12719,12 @@
       <x:c r="J16" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/songqinghai</x:v>
       </x:c>
+      <x:c r="K16" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L16" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="64" customHeight="1">
       <x:c r="A17" s="6" t="str">
@@ -11025,6 +12757,12 @@
       <x:c r="J17" s="6" t="str">
         <x:v>https://facultyprofiles.hkust.edu.hk/profiles.php?profile=andrew-wing-on-poon-eeawpoon</x:v>
       </x:c>
+      <x:c r="K17" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L17" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
       <x:c r="A18" s="6" t="str">
@@ -11057,6 +12795,12 @@
       <x:c r="J18" s="6" t="str">
         <x:v>https://chemistry.berkeley.edu/node/2571</x:v>
       </x:c>
+      <x:c r="K18" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L18" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="64" customHeight="1">
       <x:c r="A19" s="6" t="str">
@@ -11089,6 +12833,12 @@
       <x:c r="J19" s="6" t="str">
         <x:v>https://www4.mae.cuhk.edu.hk/peoples/zhang-li/</x:v>
       </x:c>
+      <x:c r="K19" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L19" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="64" customHeight="1">
       <x:c r="A20" s="6" t="str">
@@ -11121,6 +12871,12 @@
       <x:c r="J20" s="6" t="str">
         <x:v>https://samueli.ucla.edu/people/aydogan-ozcan/</x:v>
       </x:c>
+      <x:c r="K20" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L20" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="64" customHeight="1">
       <x:c r="A21" s="6" t="str">
@@ -11153,6 +12909,12 @@
       <x:c r="J21" s="6" t="str">
         <x:v>https://engineering.purdue.edu/Engr/People/ptProfile?resource_id=3198</x:v>
       </x:c>
+      <x:c r="K21" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L21" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="64" customHeight="1">
       <x:c r="A22" s="6" t="str">
@@ -11185,6 +12947,12 @@
       <x:c r="J22" s="6" t="str">
         <x:v>https://ap.polyu.edu.hk/ychai/</x:v>
       </x:c>
+      <x:c r="K22" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L22" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="64" customHeight="1">
       <x:c r="A23" s="6" t="str">
@@ -11217,6 +12985,12 @@
       <x:c r="J23" s="6" t="str">
         <x:v>https://www3.ntu.edu.sg/home/echchang/home.htm</x:v>
       </x:c>
+      <x:c r="K23" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L23" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="64" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -11245,6 +13019,12 @@
         <x:v>https://etd.ohiolink.edu/acprod/odb_etd/ws/send_file/send?accession=wright1166735848&amp;disposition=inline</x:v>
       </x:c>
       <x:c r="J24" s="6" t="str"/>
+      <x:c r="K24" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L24" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="64" customHeight="1">
       <x:c r="A25" s="6" t="str">
@@ -11277,6 +13057,12 @@
       <x:c r="J25" s="6" t="str">
         <x:v>https://www.hit.edu.cn/2024/1203/c11326a236957/page.htm</x:v>
       </x:c>
+      <x:c r="K25" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L25" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="64" customHeight="1">
       <x:c r="A26" s="6" t="str">
@@ -11309,6 +13095,12 @@
       <x:c r="J26" s="6" t="str">
         <x:v>https://iapme.um.edu.mo/people/academic-staff/xing-guichuan/</x:v>
       </x:c>
+      <x:c r="K26" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L26" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="6" t="str">
@@ -11341,6 +13133,12 @@
       <x:c r="J27" s="6" t="str">
         <x:v>https://iac.hit.edu.cn/xstd/list.htm</x:v>
       </x:c>
+      <x:c r="K27" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L27" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="64" customHeight="1">
       <x:c r="A28" s="6" t="str">
@@ -11373,6 +13171,12 @@
       <x:c r="J28" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/ouyangjiahu</x:v>
       </x:c>
+      <x:c r="K28" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L28" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="64" customHeight="1">
       <x:c r="A29" s="6" t="str">
@@ -11405,6 +13209,12 @@
       <x:c r="J29" s="6" t="str">
         <x:v>https://uwaterloo.ca/systems-design-engineering/profile/jyeow</x:v>
       </x:c>
+      <x:c r="K29" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L29" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="64" customHeight="1">
       <x:c r="A30" s="6" t="str">
@@ -11437,6 +13247,12 @@
       <x:c r="J30" s="6" t="str">
         <x:v>https://uwaterloo.ca/systems-design-engineering/profile/jyeow</x:v>
       </x:c>
+      <x:c r="K30" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L30" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="64" customHeight="1">
       <x:c r="A31" s="6" t="str">
@@ -11469,6 +13285,12 @@
       <x:c r="J31" s="6" t="str">
         <x:v>https://matsci.ucsd.edu/faculty/oscar-vazquez-mena</x:v>
       </x:c>
+      <x:c r="K31" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L31" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="64" customHeight="1">
       <x:c r="A32" s="6" t="str">
@@ -11499,6 +13321,12 @@
       <x:c r="J32" s="6" t="str">
         <x:v>https://edepot.wur.nl/283900</x:v>
       </x:c>
+      <x:c r="K32" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L32" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="64" customHeight="1">
       <x:c r="A33" s="6" t="str">
@@ -11529,6 +13357,12 @@
       <x:c r="J33" s="6" t="str">
         <x:v>https://research.wur.nl/en/persons/jasper-van-der-gucht/</x:v>
       </x:c>
+      <x:c r="K33" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L33" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="64" customHeight="1">
       <x:c r="A34" s="6" t="str">
@@ -11559,11 +13393,17 @@
       <x:c r="J34" s="6" t="str">
         <x:v>https://www.wur.nl/nl/personen/profdrir-jhb-joris-sprakel</x:v>
       </x:c>
+      <x:c r="K34" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L34" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf65ac0efcdd64039"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd4dfcc3056b4642"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11582,6 +13422,8 @@
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="55" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -11615,6 +13457,12 @@
       <x:c r="J1" s="9" t="str">
         <x:v>备注</x:v>
       </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="L1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -11645,6 +13493,12 @@
         <x:v>article_metadata_verified</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -11675,6 +13529,12 @@
         <x:v>article_metadata_verified</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str"/>
+      <x:c r="K3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -11705,6 +13565,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J4" s="6" t="str"/>
+      <x:c r="K4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -11735,6 +13601,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J5" s="6" t="str"/>
+      <x:c r="K5" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -11765,6 +13637,12 @@
         <x:v>article_metadata_verified</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str"/>
+      <x:c r="K6" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -11795,6 +13673,12 @@
       <x:c r="J7" s="6" t="str">
         <x:v>官方列212:109574；本批未核到独立论文页/DOI，链接为官方成果清单。</x:v>
       </x:c>
+      <x:c r="K7" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L7" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -11827,6 +13711,12 @@
       <x:c r="J8" s="6" t="str">
         <x:v>卷期2024；在线首发2023-12-19。</x:v>
       </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L8" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -11857,6 +13747,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J9" s="6" t="str"/>
+      <x:c r="K9" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L9" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -11887,6 +13783,12 @@
         <x:v>article_metadata_verified</x:v>
       </x:c>
       <x:c r="J10" s="6" t="str"/>
+      <x:c r="K10" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L10" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -11919,6 +13821,12 @@
       <x:c r="J11" s="6" t="str">
         <x:v>PubMed搜索索引可读，直接打开触发浏览器检查；未绕过。</x:v>
       </x:c>
+      <x:c r="K11" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L11" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -11949,6 +13857,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J12" s="6" t="str"/>
+      <x:c r="K12" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L12" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -11979,6 +13893,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J13" s="6" t="str"/>
+      <x:c r="K13" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L13" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -12009,6 +13929,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J14" s="6" t="str"/>
+      <x:c r="K14" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L14" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
       <x:c r="A15" s="6" t="str">
@@ -12037,6 +13963,12 @@
         <x:v>institutional_thesis_record_read</x:v>
       </x:c>
       <x:c r="J15" s="6" t="str"/>
+      <x:c r="K15" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L15" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="64" customHeight="1">
       <x:c r="A16" s="6" t="str">
@@ -12069,6 +14001,12 @@
       <x:c r="J16" s="6" t="str">
         <x:v>论文链接与DOI由官网明确列示；直接打开出版商链接遇认证重定向错误，未绕过。</x:v>
       </x:c>
+      <x:c r="K16" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L16" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="64" customHeight="1">
       <x:c r="A17" s="6" t="str">
@@ -12099,6 +14037,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J17" s="6" t="str"/>
+      <x:c r="K17" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L17" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
       <x:c r="A18" s="6" t="str">
@@ -12129,6 +14073,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J18" s="6" t="str"/>
+      <x:c r="K18" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L18" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="64" customHeight="1">
       <x:c r="A19" s="6" t="str">
@@ -12159,6 +14109,12 @@
       <x:c r="J19" s="6" t="str">
         <x:v>官网列17:23249–23262；独立DOI待核。</x:v>
       </x:c>
+      <x:c r="K19" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L19" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="64" customHeight="1">
       <x:c r="A20" s="6" t="str">
@@ -12189,6 +14145,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J20" s="6" t="str"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L20" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="64" customHeight="1">
       <x:c r="A21" s="6" t="str">
@@ -12219,6 +14181,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J21" s="6" t="str"/>
+      <x:c r="K21" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L21" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="64" customHeight="1">
       <x:c r="A22" s="6" t="str">
@@ -12249,6 +14217,12 @@
       <x:c r="J22" s="6" t="str">
         <x:v>学校新闻给题名与导师；年份来自官网博士毕业2020，非论文库正式题录。</x:v>
       </x:c>
+      <x:c r="K22" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L22" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="64" customHeight="1">
       <x:c r="A23" s="6" t="str">
@@ -12279,6 +14253,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J23" s="6" t="str"/>
+      <x:c r="K23" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L23" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="64" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -12309,6 +14289,12 @@
       <x:c r="J24" s="6" t="str">
         <x:v>2016-08-15答辩公告，明确作者Jiawei WANG与Thesis Supervisor；不是授位日期。</x:v>
       </x:c>
+      <x:c r="K24" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L24" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="64" customHeight="1">
       <x:c r="A25" s="6" t="str">
@@ -12339,6 +14325,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J25" s="6" t="str"/>
+      <x:c r="K25" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L25" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="64" customHeight="1">
       <x:c r="A26" s="6" t="str">
@@ -12369,6 +14361,12 @@
         <x:v>article_metadata_verified</x:v>
       </x:c>
       <x:c r="J26" s="6" t="str"/>
+      <x:c r="K26" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L26" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="6" t="str">
@@ -12401,6 +14399,12 @@
       <x:c r="J27" s="6" t="str">
         <x:v>PubMed检索题录明确作者、期刊、年卷页与DOI；直接页面正文读取不完整。</x:v>
       </x:c>
+      <x:c r="K27" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L27" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="64" customHeight="1">
       <x:c r="A28" s="6" t="str">
@@ -12431,6 +14435,12 @@
         <x:v>article_metadata_verified</x:v>
       </x:c>
       <x:c r="J28" s="6" t="str"/>
+      <x:c r="K28" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L28" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="64" customHeight="1">
       <x:c r="A29" s="6" t="str">
@@ -12461,6 +14471,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J29" s="6" t="str"/>
+      <x:c r="K29" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L29" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="64" customHeight="1">
       <x:c r="A30" s="6" t="str">
@@ -12491,6 +14507,12 @@
       <x:c r="J30" s="6" t="str">
         <x:v>题名采用本人官网；导师官网略用展开名称intellectual property protection，未取得独立论文库链接。</x:v>
       </x:c>
+      <x:c r="K30" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L30" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="64" customHeight="1">
       <x:c r="A31" s="6" t="str">
@@ -12521,6 +14543,12 @@
       <x:c r="J31" s="6" t="str">
         <x:v>封面学士院校名称与现官网存在历史名称差异；2006-11-08为批准页日期，不当授位日。</x:v>
       </x:c>
+      <x:c r="K31" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L31" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="64" customHeight="1">
       <x:c r="A32" s="6" t="str">
@@ -12551,6 +14579,12 @@
         <x:v>doi_explicitly_listed_on_official_profile</x:v>
       </x:c>
       <x:c r="J32" s="6" t="str"/>
+      <x:c r="K32" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L32" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="64" customHeight="1">
       <x:c r="A33" s="6" t="str">
@@ -12582,6 +14616,12 @@
       </x:c>
       <x:c r="J33" s="6" t="str">
         <x:v>DOI为官方主页明确列示，未独立打开出版社。</x:v>
+      </x:c>
+      <x:c r="K33" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L33" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="64" customHeight="1">
@@ -12611,6 +14651,12 @@
       <x:c r="J34" s="6" t="str">
         <x:v>官网列24(40):12612–12619。</x:v>
       </x:c>
+      <x:c r="K34" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L34" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="64" customHeight="1">
       <x:c r="A35" s="6" t="str">
@@ -12641,6 +14687,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J35" s="6" t="str"/>
+      <x:c r="K35" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L35" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="64" customHeight="1">
       <x:c r="A36" s="6" t="str">
@@ -12671,6 +14723,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J36" s="6" t="str"/>
+      <x:c r="K36" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L36" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="64" customHeight="1">
       <x:c r="A37" s="6" t="str">
@@ -12699,6 +14757,12 @@
       <x:c r="J37" s="6" t="str">
         <x:v>官网列267:61–67。</x:v>
       </x:c>
+      <x:c r="K37" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L37" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="64" customHeight="1">
       <x:c r="A38" s="6" t="str">
@@ -12729,6 +14793,12 @@
       <x:c r="J38" s="6" t="str">
         <x:v>库日期2019-09-23，不能自动等同学位授予日。</x:v>
       </x:c>
+      <x:c r="K38" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L38" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="64" customHeight="1">
       <x:c r="A39" s="6" t="str">
@@ -12761,6 +14831,12 @@
       <x:c r="J39" s="6" t="str">
         <x:v>官网卷年2020，DOI含2019为在线出版年线索，非冲突性推断。</x:v>
       </x:c>
+      <x:c r="K39" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L39" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="64" customHeight="1">
       <x:c r="A40" s="6" t="str">
@@ -12789,6 +14865,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J40" s="6" t="str"/>
+      <x:c r="K40" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L40" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="64" customHeight="1">
       <x:c r="A41" s="6" t="str">
@@ -12817,6 +14899,12 @@
       <x:c r="J41" s="6" t="str">
         <x:v>官方主页列文章号1807894；不由文章号推造DOI。</x:v>
       </x:c>
+      <x:c r="K41" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L41" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="64" customHeight="1">
       <x:c r="A42" s="6" t="str">
@@ -12845,6 +14933,12 @@
       <x:c r="J42" s="6" t="str">
         <x:v>官方主页列32:2110625。</x:v>
       </x:c>
+      <x:c r="K42" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L42" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="64" customHeight="1">
       <x:c r="A43" s="6" t="str">
@@ -12875,6 +14969,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J43" s="6" t="str"/>
+      <x:c r="K43" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L43" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="64" customHeight="1">
       <x:c r="A44" s="6" t="str">
@@ -12905,6 +15005,12 @@
       <x:c r="J44" s="6" t="str">
         <x:v>原始学位论文搜索索引可读，授位机构原始库链接尚未定位。</x:v>
       </x:c>
+      <x:c r="K44" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L44" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="64" customHeight="1">
       <x:c r="A45" s="6" t="str">
@@ -12935,6 +15041,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J45" s="6" t="str"/>
+      <x:c r="K45" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L45" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="64" customHeight="1">
       <x:c r="A46" s="6" t="str">
@@ -12965,6 +15077,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J46" s="6" t="str"/>
+      <x:c r="K46" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L46" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="64" customHeight="1">
       <x:c r="A47" s="6" t="str">
@@ -12995,6 +15113,12 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J47" s="6" t="str"/>
+      <x:c r="K47" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L47" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="64" customHeight="1">
       <x:c r="A48" s="6" t="str">
@@ -13025,11 +15149,17 @@
         <x:v>publisher_or_institutional_metadata_verified</x:v>
       </x:c>
       <x:c r="J48" s="6" t="str"/>
+      <x:c r="K48" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L48" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb70144793213466e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41e22825cfc4483a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13043,6 +15173,8 @@
     <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -13061,6 +15193,12 @@
       <x:c r="E1" s="9" t="str">
         <x:v>查阅日期</x:v>
       </x:c>
+      <x:c r="F1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="G1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -13078,6 +15216,12 @@
       <x:c r="E2" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -13095,6 +15239,12 @@
       <x:c r="E3" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -13112,6 +15262,12 @@
       <x:c r="E4" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -13129,6 +15285,12 @@
       <x:c r="E5" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -13146,6 +15308,12 @@
       <x:c r="E6" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -13163,6 +15331,12 @@
       <x:c r="E7" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -13180,6 +15354,12 @@
       <x:c r="E8" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -13197,6 +15377,12 @@
       <x:c r="E9" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -13214,6 +15400,12 @@
       <x:c r="E10" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -13231,6 +15423,12 @@
       <x:c r="E11" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -13248,6 +15446,12 @@
       <x:c r="E12" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -13265,6 +15469,12 @@
       <x:c r="E13" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -13282,6 +15492,12 @@
       <x:c r="E14" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
       <x:c r="A15" s="6" t="str">
@@ -13299,6 +15515,12 @@
       <x:c r="E15" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="64" customHeight="1">
       <x:c r="A16" s="6" t="str">
@@ -13316,6 +15538,12 @@
       <x:c r="E16" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="64" customHeight="1">
       <x:c r="A17" s="6" t="str">
@@ -13333,6 +15561,12 @@
       <x:c r="E17" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G17" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
       <x:c r="A18" s="6" t="str">
@@ -13350,6 +15584,12 @@
       <x:c r="E18" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F18" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="64" customHeight="1">
       <x:c r="A19" s="6" t="str">
@@ -13367,6 +15607,12 @@
       <x:c r="E19" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G19" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="64" customHeight="1">
       <x:c r="A20" s="6" t="str">
@@ -13384,6 +15630,12 @@
       <x:c r="E20" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="64" customHeight="1">
       <x:c r="A21" s="6" t="str">
@@ -13401,6 +15653,12 @@
       <x:c r="E21" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G21" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="64" customHeight="1">
       <x:c r="A22" s="6" t="str">
@@ -13418,6 +15676,12 @@
       <x:c r="E22" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F22" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="64" customHeight="1">
       <x:c r="A23" s="6" t="str">
@@ -13435,6 +15699,12 @@
       <x:c r="E23" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="64" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -13452,6 +15722,12 @@
       <x:c r="E24" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="64" customHeight="1">
       <x:c r="A25" s="6" t="str">
@@ -13469,6 +15745,12 @@
       <x:c r="E25" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F25" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="64" customHeight="1">
       <x:c r="A26" s="6" t="str">
@@ -13486,6 +15768,12 @@
       <x:c r="E26" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F26" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="64" customHeight="1">
       <x:c r="A27" s="6" t="str">
@@ -13503,6 +15791,12 @@
       <x:c r="E27" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="64" customHeight="1">
       <x:c r="A28" s="6" t="str">
@@ -13520,6 +15814,12 @@
       <x:c r="E28" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="64" customHeight="1">
       <x:c r="A29" s="6" t="str">
@@ -13537,6 +15837,12 @@
       <x:c r="E29" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F29" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G29" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="64" customHeight="1">
       <x:c r="A30" s="6" t="str">
@@ -13554,6 +15860,12 @@
       <x:c r="E30" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F30" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G30" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="64" customHeight="1">
       <x:c r="A31" s="6" t="str">
@@ -13571,6 +15883,12 @@
       <x:c r="E31" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F31" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G31" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="64" customHeight="1">
       <x:c r="A32" s="6" t="str">
@@ -13588,6 +15906,12 @@
       <x:c r="E32" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F32" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G32" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="64" customHeight="1">
       <x:c r="A33" s="6" t="str">
@@ -13605,6 +15929,12 @@
       <x:c r="E33" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F33" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G33" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="64" customHeight="1">
       <x:c r="A34" s="6" t="str">
@@ -13622,6 +15952,12 @@
       <x:c r="E34" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F34" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G34" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="64" customHeight="1">
       <x:c r="A35" s="6" t="str">
@@ -13639,6 +15975,12 @@
       <x:c r="E35" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F35" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G35" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="64" customHeight="1">
       <x:c r="A36" s="6" t="str">
@@ -13656,6 +15998,12 @@
       <x:c r="E36" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F36" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G36" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="64" customHeight="1">
       <x:c r="A37" s="6" t="str">
@@ -13673,6 +16021,12 @@
       <x:c r="E37" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F37" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G37" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="64" customHeight="1">
       <x:c r="A38" s="6" t="str">
@@ -13690,6 +16044,12 @@
       <x:c r="E38" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="64" customHeight="1">
       <x:c r="A39" s="6" t="str">
@@ -13707,6 +16067,12 @@
       <x:c r="E39" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="64" customHeight="1">
       <x:c r="A40" s="6" t="str">
@@ -13724,6 +16090,12 @@
       <x:c r="E40" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="64" customHeight="1">
       <x:c r="A41" s="6" t="str">
@@ -13741,6 +16113,12 @@
       <x:c r="E41" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F41" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G41" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="64" customHeight="1">
       <x:c r="A42" s="6" t="str">
@@ -13758,6 +16136,12 @@
       <x:c r="E42" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F42" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="64" customHeight="1">
       <x:c r="A43" s="6" t="str">
@@ -13775,6 +16159,12 @@
       <x:c r="E43" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="64" customHeight="1">
       <x:c r="A44" s="6" t="str">
@@ -13792,6 +16182,12 @@
       <x:c r="E44" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="64" customHeight="1">
       <x:c r="A45" s="6" t="str">
@@ -13809,6 +16205,12 @@
       <x:c r="E45" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="64" customHeight="1">
       <x:c r="A46" s="6" t="str">
@@ -13826,6 +16228,12 @@
       <x:c r="E46" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F46" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G46" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="64" customHeight="1">
       <x:c r="A47" s="6" t="str">
@@ -13843,6 +16251,12 @@
       <x:c r="E47" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F47" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="64" customHeight="1">
       <x:c r="A48" s="6" t="str">
@@ -13860,6 +16274,12 @@
       <x:c r="E48" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F48" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="64" customHeight="1">
       <x:c r="A49" s="6" t="str">
@@ -13877,6 +16297,12 @@
       <x:c r="E49" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F49" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="64" customHeight="1">
       <x:c r="A50" s="6" t="str">
@@ -13894,6 +16320,12 @@
       <x:c r="E50" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F50" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G50" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="64" customHeight="1">
       <x:c r="A51" s="6" t="str">
@@ -13911,6 +16343,12 @@
       <x:c r="E51" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F51" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G51" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="64" customHeight="1">
       <x:c r="A52" s="6" t="str">
@@ -13928,6 +16366,12 @@
       <x:c r="E52" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F52" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G52" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="64" customHeight="1">
       <x:c r="A53" s="6" t="str">
@@ -13945,6 +16389,12 @@
       <x:c r="E53" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F53" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G53" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="64" customHeight="1">
       <x:c r="A54" s="6" t="str">
@@ -13962,6 +16412,12 @@
       <x:c r="E54" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F54" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="64" customHeight="1">
       <x:c r="A55" s="6" t="str">
@@ -13979,6 +16435,12 @@
       <x:c r="E55" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F55" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G55" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="64" customHeight="1">
       <x:c r="A56" s="6" t="str">
@@ -13996,6 +16458,12 @@
       <x:c r="E56" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F56" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G56" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="64" customHeight="1">
       <x:c r="A57" s="6" t="str">
@@ -14013,6 +16481,12 @@
       <x:c r="E57" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F57" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G57" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="64" customHeight="1">
       <x:c r="A58" s="6" t="str">
@@ -14030,6 +16504,12 @@
       <x:c r="E58" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F58" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G58" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="64" customHeight="1">
       <x:c r="A59" s="6" t="str">
@@ -14047,6 +16527,12 @@
       <x:c r="E59" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F59" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G59" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="64" customHeight="1">
       <x:c r="A60" s="6" t="str">
@@ -14064,6 +16550,12 @@
       <x:c r="E60" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F60" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G60" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="64" customHeight="1">
       <x:c r="A61" s="6" t="str">
@@ -14081,6 +16573,12 @@
       <x:c r="E61" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F61" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G61" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="64" customHeight="1">
       <x:c r="A62" s="6" t="str">
@@ -14098,6 +16596,12 @@
       <x:c r="E62" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F62" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G62" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="64" customHeight="1">
       <x:c r="A63" s="6" t="str">
@@ -14115,6 +16619,12 @@
       <x:c r="E63" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F63" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G63" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="64" customHeight="1">
       <x:c r="A64" s="6" t="str">
@@ -14132,6 +16642,12 @@
       <x:c r="E64" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F64" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G64" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="64" customHeight="1">
       <x:c r="A65" s="6" t="str">
@@ -14149,6 +16665,12 @@
       <x:c r="E65" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F65" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G65" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="64" customHeight="1">
       <x:c r="A66" s="6" t="str">
@@ -14166,6 +16688,12 @@
       <x:c r="E66" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F66" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G66" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="64" customHeight="1">
       <x:c r="A67" s="6" t="str">
@@ -14183,6 +16711,12 @@
       <x:c r="E67" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F67" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G67" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="64" customHeight="1">
       <x:c r="A68" s="6" t="str">
@@ -14200,6 +16734,12 @@
       <x:c r="E68" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F68" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G68" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="64" customHeight="1">
       <x:c r="A69" s="6" t="str">
@@ -14217,6 +16757,12 @@
       <x:c r="E69" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F69" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G69" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="64" customHeight="1">
       <x:c r="A70" s="6" t="str">
@@ -14234,6 +16780,12 @@
       <x:c r="E70" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F70" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G70" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="64" customHeight="1">
       <x:c r="A71" s="6" t="str">
@@ -14251,6 +16803,12 @@
       <x:c r="E71" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F71" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G71" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="64" customHeight="1">
       <x:c r="A72" s="6" t="str">
@@ -14268,6 +16826,12 @@
       <x:c r="E72" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F72" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G72" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="64" customHeight="1">
       <x:c r="A73" s="6" t="str">
@@ -14285,6 +16849,12 @@
       <x:c r="E73" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F73" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G73" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="64" customHeight="1">
       <x:c r="A74" s="6" t="str">
@@ -14302,6 +16872,12 @@
       <x:c r="E74" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F74" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G74" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="64" customHeight="1">
       <x:c r="A75" s="6" t="str">
@@ -14319,6 +16895,12 @@
       <x:c r="E75" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F75" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G75" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="64" customHeight="1">
       <x:c r="A76" s="6" t="str">
@@ -14336,6 +16918,12 @@
       <x:c r="E76" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F76" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G76" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="64" customHeight="1">
       <x:c r="A77" s="6" t="str">
@@ -14353,6 +16941,12 @@
       <x:c r="E77" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F77" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G77" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="64" customHeight="1">
       <x:c r="A78" s="6" t="str">
@@ -14370,6 +16964,12 @@
       <x:c r="E78" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F78" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G78" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="64" customHeight="1">
       <x:c r="A79" s="6" t="str">
@@ -14387,6 +16987,12 @@
       <x:c r="E79" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F79" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G79" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="64" customHeight="1">
       <x:c r="A80" s="6" t="str">
@@ -14404,6 +17010,12 @@
       <x:c r="E80" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F80" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G80" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="64" customHeight="1">
       <x:c r="A81" s="6" t="str">
@@ -14421,6 +17033,12 @@
       <x:c r="E81" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F81" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G81" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="64" customHeight="1">
       <x:c r="A82" s="6" t="str">
@@ -14438,6 +17056,12 @@
       <x:c r="E82" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F82" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G82" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="64" customHeight="1">
       <x:c r="A83" s="6" t="str">
@@ -14455,6 +17079,12 @@
       <x:c r="E83" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F83" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G83" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="64" customHeight="1">
       <x:c r="A84" s="6" t="str">
@@ -14472,6 +17102,12 @@
       <x:c r="E84" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F84" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G84" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="64" customHeight="1">
       <x:c r="A85" s="6" t="str">
@@ -14489,6 +17125,12 @@
       <x:c r="E85" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F85" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G85" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="64" customHeight="1">
       <x:c r="A86" s="6" t="str">
@@ -14506,6 +17148,12 @@
       <x:c r="E86" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F86" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G86" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="64" customHeight="1">
       <x:c r="A87" s="6" t="str">
@@ -14523,6 +17171,12 @@
       <x:c r="E87" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F87" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G87" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="64" customHeight="1">
       <x:c r="A88" s="6" t="str">
@@ -14540,6 +17194,12 @@
       <x:c r="E88" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F88" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G88" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="64" customHeight="1">
       <x:c r="A89" s="6" t="str">
@@ -14557,6 +17217,12 @@
       <x:c r="E89" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F89" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G89" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="64" customHeight="1">
       <x:c r="A90" s="6" t="str">
@@ -14574,6 +17240,12 @@
       <x:c r="E90" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F90" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G90" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="91" ht="64" customHeight="1">
       <x:c r="A91" s="6" t="str">
@@ -14591,6 +17263,12 @@
       <x:c r="E91" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F91" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G91" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="92" ht="64" customHeight="1">
       <x:c r="A92" s="6" t="str">
@@ -14608,6 +17286,12 @@
       <x:c r="E92" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F92" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G92" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" ht="64" customHeight="1">
       <x:c r="A93" s="6" t="str">
@@ -14625,6 +17309,12 @@
       <x:c r="E93" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F93" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G93" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="94" ht="64" customHeight="1">
       <x:c r="A94" s="6" t="str">
@@ -14642,6 +17332,12 @@
       <x:c r="E94" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F94" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G94" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="95" ht="64" customHeight="1">
       <x:c r="A95" s="6" t="str">
@@ -14659,6 +17355,12 @@
       <x:c r="E95" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F95" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G95" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="96" ht="64" customHeight="1">
       <x:c r="A96" s="6" t="str">
@@ -14676,6 +17378,12 @@
       <x:c r="E96" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F96" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G96" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="97" ht="64" customHeight="1">
       <x:c r="A97" s="6" t="str">
@@ -14693,6 +17401,12 @@
       <x:c r="E97" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F97" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G97" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="98" ht="64" customHeight="1">
       <x:c r="A98" s="6" t="str">
@@ -14710,6 +17424,12 @@
       <x:c r="E98" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F98" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G98" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="99" ht="64" customHeight="1">
       <x:c r="A99" s="6" t="str">
@@ -14727,6 +17447,12 @@
       <x:c r="E99" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F99" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G99" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" ht="64" customHeight="1">
       <x:c r="A100" s="6" t="str">
@@ -14744,6 +17470,12 @@
       <x:c r="E100" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F100" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G100" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="101" ht="64" customHeight="1">
       <x:c r="A101" s="6" t="str">
@@ -14761,6 +17493,12 @@
       <x:c r="E101" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F101" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G101" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="64" customHeight="1">
       <x:c r="A102" s="6" t="str">
@@ -14778,6 +17516,12 @@
       <x:c r="E102" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F102" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G102" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="64" customHeight="1">
       <x:c r="A103" s="6" t="str">
@@ -14795,6 +17539,12 @@
       <x:c r="E103" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F103" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G103" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" ht="64" customHeight="1">
       <x:c r="A104" s="6" t="str">
@@ -14812,6 +17562,12 @@
       <x:c r="E104" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F104" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G104" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="64" customHeight="1">
       <x:c r="A105" s="6" t="str">
@@ -14829,6 +17585,12 @@
       <x:c r="E105" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F105" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G105" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" ht="64" customHeight="1">
       <x:c r="A106" s="6" t="str">
@@ -14846,6 +17608,12 @@
       <x:c r="E106" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F106" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G106" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="64" customHeight="1">
       <x:c r="A107" s="6" t="str">
@@ -14863,6 +17631,12 @@
       <x:c r="E107" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F107" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G107" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" ht="64" customHeight="1">
       <x:c r="A108" s="6" t="str">
@@ -14880,6 +17654,12 @@
       <x:c r="E108" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F108" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G108" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" ht="64" customHeight="1">
       <x:c r="A109" s="6" t="str">
@@ -14897,6 +17677,12 @@
       <x:c r="E109" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F109" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G109" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" ht="64" customHeight="1">
       <x:c r="A110" s="6" t="str">
@@ -14914,6 +17700,12 @@
       <x:c r="E110" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F110" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G110" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" ht="64" customHeight="1">
       <x:c r="A111" s="6" t="str">
@@ -14931,6 +17723,12 @@
       <x:c r="E111" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F111" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G111" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="112" ht="64" customHeight="1">
       <x:c r="A112" s="6" t="str">
@@ -14948,6 +17746,12 @@
       <x:c r="E112" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F112" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G112" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="113" ht="64" customHeight="1">
       <x:c r="A113" s="6" t="str">
@@ -14965,6 +17769,12 @@
       <x:c r="E113" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F113" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G113" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="114" ht="64" customHeight="1">
       <x:c r="A114" s="6" t="str">
@@ -14982,6 +17792,12 @@
       <x:c r="E114" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F114" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G114" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" ht="64" customHeight="1">
       <x:c r="A115" s="6" t="str">
@@ -14999,6 +17815,12 @@
       <x:c r="E115" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F115" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G115" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" ht="64" customHeight="1">
       <x:c r="A116" s="6" t="str">
@@ -15016,6 +17838,12 @@
       <x:c r="E116" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F116" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G116" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" ht="64" customHeight="1">
       <x:c r="A117" s="6" t="str">
@@ -15033,6 +17861,12 @@
       <x:c r="E117" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F117" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G117" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" ht="64" customHeight="1">
       <x:c r="A118" s="6" t="str">
@@ -15050,6 +17884,12 @@
       <x:c r="E118" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F118" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G118" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="119" ht="64" customHeight="1">
       <x:c r="A119" s="6" t="str">
@@ -15067,6 +17907,12 @@
       <x:c r="E119" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F119" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G119" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" ht="64" customHeight="1">
       <x:c r="A120" s="6" t="str">
@@ -15084,6 +17930,12 @@
       <x:c r="E120" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F120" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G120" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="121" ht="64" customHeight="1">
       <x:c r="A121" s="6" t="str">
@@ -15101,6 +17953,12 @@
       <x:c r="E121" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F121" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G121" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="122" ht="64" customHeight="1">
       <x:c r="A122" s="6" t="str">
@@ -15118,6 +17976,12 @@
       <x:c r="E122" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F122" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G122" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="123" ht="64" customHeight="1">
       <x:c r="A123" s="6" t="str">
@@ -15135,6 +17999,12 @@
       <x:c r="E123" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F123" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G123" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="124" ht="64" customHeight="1">
       <x:c r="A124" s="6" t="str">
@@ -15152,6 +18022,12 @@
       <x:c r="E124" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F124" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G124" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="125" ht="64" customHeight="1">
       <x:c r="A125" s="6" t="str">
@@ -15169,6 +18045,12 @@
       <x:c r="E125" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F125" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G125" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="64" customHeight="1">
       <x:c r="A126" s="6" t="str">
@@ -15186,6 +18068,12 @@
       <x:c r="E126" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F126" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G126" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="127" ht="64" customHeight="1">
       <x:c r="A127" s="6" t="str">
@@ -15203,6 +18091,12 @@
       <x:c r="E127" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F127" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G127" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="128" ht="64" customHeight="1">
       <x:c r="A128" s="6" t="str">
@@ -15220,6 +18114,12 @@
       <x:c r="E128" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F128" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G128" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" ht="64" customHeight="1">
       <x:c r="A129" s="6" t="str">
@@ -15237,6 +18137,12 @@
       <x:c r="E129" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F129" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G129" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="64" customHeight="1">
       <x:c r="A130" s="6" t="str">
@@ -15254,6 +18160,12 @@
       <x:c r="E130" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F130" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G130" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" ht="64" customHeight="1">
       <x:c r="A131" s="6" t="str">
@@ -15271,6 +18183,12 @@
       <x:c r="E131" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F131" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G131" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="132" ht="64" customHeight="1">
       <x:c r="A132" s="6" t="str">
@@ -15288,6 +18206,12 @@
       <x:c r="E132" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F132" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G132" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="133" ht="64" customHeight="1">
       <x:c r="A133" s="6" t="str">
@@ -15305,6 +18229,12 @@
       <x:c r="E133" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F133" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G133" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="134" ht="64" customHeight="1">
       <x:c r="A134" s="6" t="str">
@@ -15322,6 +18252,12 @@
       <x:c r="E134" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F134" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G134" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="135" ht="64" customHeight="1">
       <x:c r="A135" s="6" t="str">
@@ -15339,6 +18275,12 @@
       <x:c r="E135" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F135" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G135" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="136" ht="64" customHeight="1">
       <x:c r="A136" s="6" t="str">
@@ -15356,6 +18298,12 @@
       <x:c r="E136" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F136" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G136" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" ht="64" customHeight="1">
       <x:c r="A137" s="6" t="str">
@@ -15373,6 +18321,12 @@
       <x:c r="E137" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F137" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G137" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="138" ht="64" customHeight="1">
       <x:c r="A138" s="6" t="str">
@@ -15390,6 +18344,12 @@
       <x:c r="E138" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F138" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G138" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="139" ht="64" customHeight="1">
       <x:c r="A139" s="6" t="str">
@@ -15407,6 +18367,12 @@
       <x:c r="E139" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F139" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G139" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="140" ht="64" customHeight="1">
       <x:c r="A140" s="6" t="str">
@@ -15424,6 +18390,12 @@
       <x:c r="E140" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F140" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G140" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="141" ht="64" customHeight="1">
       <x:c r="A141" s="6" t="str">
@@ -15441,6 +18413,12 @@
       <x:c r="E141" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F141" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G141" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="142" ht="64" customHeight="1">
       <x:c r="A142" s="6" t="str">
@@ -15458,6 +18436,12 @@
       <x:c r="E142" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F142" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G142" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="143" ht="64" customHeight="1">
       <x:c r="A143" s="6" t="str">
@@ -15475,6 +18459,12 @@
       <x:c r="E143" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F143" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G143" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="144" ht="64" customHeight="1">
       <x:c r="A144" s="6" t="str">
@@ -15492,6 +18482,12 @@
       <x:c r="E144" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F144" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G144" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="145" ht="64" customHeight="1">
       <x:c r="A145" s="6" t="str">
@@ -15509,6 +18505,12 @@
       <x:c r="E145" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F145" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G145" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="146" ht="64" customHeight="1">
       <x:c r="A146" s="6" t="str">
@@ -15526,6 +18528,12 @@
       <x:c r="E146" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F146" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G146" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="147" ht="64" customHeight="1">
       <x:c r="A147" s="6" t="str">
@@ -15543,6 +18551,12 @@
       <x:c r="E147" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F147" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G147" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="148" ht="64" customHeight="1">
       <x:c r="A148" s="6" t="str">
@@ -15560,6 +18574,12 @@
       <x:c r="E148" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F148" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G148" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="149" ht="64" customHeight="1">
       <x:c r="A149" s="6" t="str">
@@ -15577,6 +18597,12 @@
       <x:c r="E149" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F149" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G149" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" ht="64" customHeight="1">
       <x:c r="A150" s="6" t="str">
@@ -15594,6 +18620,12 @@
       <x:c r="E150" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F150" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G150" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="151" ht="64" customHeight="1">
       <x:c r="A151" s="6" t="str">
@@ -15611,6 +18643,12 @@
       <x:c r="E151" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F151" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G151" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="152" ht="64" customHeight="1">
       <x:c r="A152" s="6" t="str">
@@ -15628,6 +18666,12 @@
       <x:c r="E152" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F152" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G152" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="153" ht="64" customHeight="1">
       <x:c r="A153" s="6" t="str">
@@ -15645,6 +18689,12 @@
       <x:c r="E153" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F153" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G153" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="154" ht="64" customHeight="1">
       <x:c r="A154" s="6" t="str">
@@ -15662,6 +18712,12 @@
       <x:c r="E154" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F154" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G154" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="155" ht="64" customHeight="1">
       <x:c r="A155" s="6" t="str">
@@ -15679,6 +18735,12 @@
       <x:c r="E155" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F155" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G155" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="156" ht="64" customHeight="1">
       <x:c r="A156" s="6" t="str">
@@ -15696,6 +18758,12 @@
       <x:c r="E156" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F156" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G156" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="157" ht="64" customHeight="1">
       <x:c r="A157" s="6" t="str">
@@ -15713,6 +18781,12 @@
       <x:c r="E157" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F157" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G157" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="158" ht="64" customHeight="1">
       <x:c r="A158" s="6" t="str">
@@ -15730,6 +18804,12 @@
       <x:c r="E158" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F158" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G158" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="159" ht="64" customHeight="1">
       <x:c r="A159" s="6" t="str">
@@ -15747,6 +18827,12 @@
       <x:c r="E159" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F159" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G159" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="160" ht="64" customHeight="1">
       <x:c r="A160" s="6" t="str">
@@ -15764,6 +18850,12 @@
       <x:c r="E160" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F160" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G160" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="161" ht="64" customHeight="1">
       <x:c r="A161" s="6" t="str">
@@ -15781,6 +18873,12 @@
       <x:c r="E161" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F161" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G161" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="162" ht="64" customHeight="1">
       <x:c r="A162" s="6" t="str">
@@ -15798,6 +18896,12 @@
       <x:c r="E162" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F162" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G162" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="163" ht="64" customHeight="1">
       <x:c r="A163" s="6" t="str">
@@ -15815,6 +18919,12 @@
       <x:c r="E163" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F163" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G163" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="164" ht="64" customHeight="1">
       <x:c r="A164" s="6" t="str">
@@ -15832,6 +18942,12 @@
       <x:c r="E164" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F164" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G164" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="165" ht="64" customHeight="1">
       <x:c r="A165" s="6" t="str">
@@ -15849,6 +18965,12 @@
       <x:c r="E165" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F165" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G165" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="166" ht="64" customHeight="1">
       <x:c r="A166" s="6" t="str">
@@ -15866,6 +18988,12 @@
       <x:c r="E166" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F166" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G166" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="167" ht="64" customHeight="1">
       <x:c r="A167" s="6" t="str">
@@ -15883,6 +19011,12 @@
       <x:c r="E167" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F167" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G167" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="168" ht="64" customHeight="1">
       <x:c r="A168" s="6" t="str">
@@ -15900,6 +19034,12 @@
       <x:c r="E168" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F168" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G168" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="169" ht="64" customHeight="1">
       <x:c r="A169" s="6" t="str">
@@ -15917,6 +19057,12 @@
       <x:c r="E169" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F169" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G169" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="170" ht="64" customHeight="1">
       <x:c r="A170" s="6" t="str">
@@ -15934,6 +19080,12 @@
       <x:c r="E170" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F170" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G170" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="171" ht="64" customHeight="1">
       <x:c r="A171" s="6" t="str">
@@ -15951,6 +19103,12 @@
       <x:c r="E171" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F171" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G171" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="172" ht="64" customHeight="1">
       <x:c r="A172" s="6" t="str">
@@ -15968,6 +19126,12 @@
       <x:c r="E172" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F172" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G172" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="173" ht="64" customHeight="1">
       <x:c r="A173" s="6" t="str">
@@ -15985,6 +19149,12 @@
       <x:c r="E173" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F173" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G173" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="174" ht="64" customHeight="1">
       <x:c r="A174" s="6" t="str">
@@ -16002,6 +19172,12 @@
       <x:c r="E174" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F174" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G174" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="175" ht="64" customHeight="1">
       <x:c r="A175" s="6" t="str">
@@ -16019,6 +19195,12 @@
       <x:c r="E175" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F175" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G175" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="176" ht="64" customHeight="1">
       <x:c r="A176" s="6" t="str">
@@ -16036,11 +19218,17 @@
       <x:c r="E176" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F176" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G176" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87eb23c39fc04910"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a4c7af3ba16429b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-ic.xlsx
+++ b/site/exports/hit-shenzhen-ic.xlsx
@@ -452,8 +452,8 @@
     <col width="57.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -708,12 +708,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -814,12 +814,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -867,12 +867,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -920,12 +920,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -28794,7 +28794,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -28831,7 +28831,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -28868,7 +28868,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -28905,7 +28905,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -28942,7 +28942,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -29053,7 +29053,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -29201,7 +29201,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -29238,7 +29238,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -29275,7 +29275,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -29312,7 +29312,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -29423,7 +29423,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -29460,7 +29460,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -29497,7 +29497,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -29534,7 +29534,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -29571,7 +29571,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -29645,7 +29645,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -29682,7 +29682,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -29719,7 +29719,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -29793,7 +29793,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -29830,7 +29830,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -29867,7 +29867,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -29941,7 +29941,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -29978,7 +29978,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -30015,7 +30015,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
